--- a/AAII_Financials/Quarterly/DLNG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DLNG_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="92">
   <si>
     <t>DLNG</t>
   </si>
@@ -656,403 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>48600</v>
+      </c>
+      <c r="E8" s="3">
         <v>37700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>37300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>35100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>29900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>33400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>33300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>35700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>34700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>33900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>33400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>34400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>34300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>33900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>34500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>34300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>34400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>30800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>31400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>31000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>31300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>30900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>33900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>34500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>33500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>32000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>39100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>41400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>43100</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E9" s="3">
         <v>8900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7900</v>
-      </c>
-      <c r="H9" s="3">
-        <v>8200</v>
       </c>
       <c r="I9" s="3">
         <v>8200</v>
       </c>
       <c r="J9" s="3">
+        <v>8200</v>
+      </c>
+      <c r="K9" s="3">
         <v>8700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>7900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>7800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8300</v>
-      </c>
-      <c r="T9" s="3">
-        <v>7500</v>
       </c>
       <c r="U9" s="3">
         <v>7500</v>
       </c>
       <c r="V9" s="3">
+        <v>7500</v>
+      </c>
+      <c r="W9" s="3">
         <v>7000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>7400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>6500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>7000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>7400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>6900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>7500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>7400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>36800</v>
+      </c>
+      <c r="E10" s="3">
         <v>28800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>29300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>26600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>22000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>25200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>25100</v>
-      </c>
-      <c r="J10" s="3">
-        <v>27000</v>
       </c>
       <c r="K10" s="3">
         <v>27000</v>
       </c>
       <c r="L10" s="3">
+        <v>27000</v>
+      </c>
+      <c r="M10" s="3">
         <v>25600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>25800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>26600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>26400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>26300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>26000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>26500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>26100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>23300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>23900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>24000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>23900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>24400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>26900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>27100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>26600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>23200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>31600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>34000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>35600</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1173,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1279,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1271,14 +1291,14 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-2100</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1294,8 +1314,8 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1351,8 +1371,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1360,58 +1383,58 @@
         <v>8000</v>
       </c>
       <c r="E15" s="3">
+        <v>8000</v>
+      </c>
+      <c r="F15" s="3">
         <v>7900</v>
-      </c>
-      <c r="F15" s="3">
-        <v>8000</v>
       </c>
       <c r="G15" s="3">
         <v>8000</v>
       </c>
       <c r="H15" s="3">
+        <v>8000</v>
+      </c>
+      <c r="I15" s="3">
         <v>7900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7800</v>
-      </c>
-      <c r="J15" s="3">
-        <v>8000</v>
       </c>
       <c r="K15" s="3">
         <v>8000</v>
       </c>
       <c r="L15" s="3">
+        <v>8000</v>
+      </c>
+      <c r="M15" s="3">
         <v>7900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>7800</v>
-      </c>
-      <c r="N15" s="3">
-        <v>8000</v>
       </c>
       <c r="O15" s="3">
         <v>8000</v>
       </c>
       <c r="P15" s="3">
-        <v>7900</v>
+        <v>8000</v>
       </c>
       <c r="Q15" s="3">
         <v>7900</v>
       </c>
       <c r="R15" s="3">
+        <v>7900</v>
+      </c>
+      <c r="S15" s="3">
         <v>8000</v>
-      </c>
-      <c r="S15" s="3">
-        <v>7600</v>
       </c>
       <c r="T15" s="3">
         <v>7600</v>
       </c>
       <c r="U15" s="3">
+        <v>7600</v>
+      </c>
+      <c r="V15" s="3">
         <v>7500</v>
-      </c>
-      <c r="V15" s="3">
-        <v>7600</v>
       </c>
       <c r="W15" s="3">
         <v>7600</v>
@@ -1420,10 +1443,10 @@
         <v>7600</v>
       </c>
       <c r="Y15" s="3">
+        <v>7600</v>
+      </c>
+      <c r="Z15" s="3">
         <v>7500</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>7600</v>
       </c>
       <c r="AA15" s="3">
         <v>7600</v>
@@ -1432,16 +1455,19 @@
         <v>7600</v>
       </c>
       <c r="AC15" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AD15" s="3">
         <v>7500</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>7600</v>
       </c>
       <c r="AE15" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,20 +1496,21 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>39200</v>
+      </c>
+      <c r="E17" s="3">
         <v>19400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>18100</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1493,12 +1520,12 @@
       <c r="I17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J17" s="3">
+      <c r="J17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="3">
         <v>18900</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1526,53 +1553,56 @@
       <c r="T17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V17" s="3">
         <v>17000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>19300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>19400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>18300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>17100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>17000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>17600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>23200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>17200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>17100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E18" s="3">
         <v>18300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>19200</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G18" s="3" t="s">
         <v>8</v>
       </c>
@@ -1582,12 +1612,12 @@
       <c r="I18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="3">
         <v>16800</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>8</v>
       </c>
@@ -1615,41 +1645,44 @@
       <c r="T18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V18" s="3">
         <v>14400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>11700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>11900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>12600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>16800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>17500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>15900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>8800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>21900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>24300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,20 +1714,21 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-9600</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G20" s="3" t="s">
         <v>8</v>
       </c>
@@ -1704,12 +1738,12 @@
       <c r="I20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
@@ -1737,53 +1771,56 @@
       <c r="T20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V20" s="3">
         <v>500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>300</v>
-      </c>
-      <c r="W20" s="3">
-        <v>200</v>
       </c>
       <c r="X20" s="3">
         <v>200</v>
       </c>
       <c r="Y20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-100</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E21" s="3">
         <v>22400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>17500</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1793,12 +1830,12 @@
       <c r="I21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="3">
         <v>24900</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1826,41 +1863,44 @@
       <c r="T21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V21" s="3">
         <v>22400</v>
-      </c>
-      <c r="V21" s="3">
-        <v>19700</v>
       </c>
       <c r="W21" s="3">
         <v>19700</v>
       </c>
       <c r="X21" s="3">
+        <v>19700</v>
+      </c>
+      <c r="Y21" s="3">
         <v>20400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>24300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>25100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>23400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>15100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>29200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>32000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>33600</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1897,8 +1937,8 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>8</v>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>8</v>
@@ -1915,53 +1955,56 @@
       <c r="T22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U22" s="3">
-        <v>13000</v>
+      <c r="U22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V22" s="3">
         <v>13000</v>
       </c>
       <c r="W22" s="3">
+        <v>13000</v>
+      </c>
+      <c r="X22" s="3">
         <v>12700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>12500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>12000</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>11800</v>
       </c>
       <c r="AA22" s="3">
         <v>11800</v>
       </c>
       <c r="AB22" s="3">
+        <v>11800</v>
+      </c>
+      <c r="AC22" s="3">
         <v>12700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>8800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>8900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E23" s="3">
         <v>14400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>9600</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G23" s="3" t="s">
         <v>8</v>
       </c>
@@ -1971,12 +2014,12 @@
       <c r="I23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J23" s="3">
+      <c r="J23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="3">
         <v>16900</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>8</v>
       </c>
@@ -2004,41 +2047,44 @@
       <c r="T23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V23" s="3">
         <v>1900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>5600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>12900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>15500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>17300</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2126,8 +2172,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,20 +2264,23 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E26" s="3">
         <v>14400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>9600</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G26" s="3" t="s">
         <v>8</v>
       </c>
@@ -2238,12 +2290,12 @@
       <c r="I26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J26" s="3">
+      <c r="J26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="3">
         <v>16900</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>8</v>
       </c>
@@ -2271,53 +2323,56 @@
       <c r="T26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V26" s="3">
         <v>1900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>5600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>12900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>15500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>17300</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E27" s="3">
         <v>14400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>9600</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G27" s="3" t="s">
         <v>8</v>
       </c>
@@ -2327,12 +2382,12 @@
       <c r="I27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J27" s="3">
+      <c r="J27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="3">
         <v>16900</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>8</v>
       </c>
@@ -2360,41 +2415,44 @@
       <c r="T27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V27" s="3">
         <v>-1000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>10000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>7900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,20 +2816,23 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E32" s="3">
         <v>3900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>9600</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G32" s="3" t="s">
         <v>8</v>
       </c>
@@ -2772,12 +2842,12 @@
       <c r="I32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
@@ -2805,53 +2875,56 @@
       <c r="T32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V32" s="3">
         <v>-500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-300</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-200</v>
       </c>
       <c r="X32" s="3">
         <v>-200</v>
       </c>
       <c r="Y32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>100</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E33" s="3">
         <v>14400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>9600</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G33" s="3" t="s">
         <v>8</v>
       </c>
@@ -2861,12 +2934,12 @@
       <c r="I33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J33" s="3">
+      <c r="J33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" s="3">
         <v>16900</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>8</v>
       </c>
@@ -2894,41 +2967,44 @@
       <c r="T33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V33" s="3">
         <v>-1000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>10000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>7900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,20 +3092,23 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E35" s="3">
         <v>14400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>9600</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G35" s="3" t="s">
         <v>8</v>
       </c>
@@ -3039,12 +3118,12 @@
       <c r="I35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J35" s="3">
+      <c r="J35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="3">
         <v>16900</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>8</v>
       </c>
@@ -3072,135 +3151,141 @@
       <c r="T35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V35" s="3">
         <v>-1000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>10000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>7900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,97 +3351,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>52900</v>
+        <v>64900</v>
       </c>
       <c r="E41" s="3">
         <v>52900</v>
       </c>
       <c r="F41" s="3">
+        <v>52900</v>
+      </c>
+      <c r="G41" s="3">
         <v>48600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>97700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>100200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>106600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>47000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>91300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>86800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>84100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>25000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>76000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>63300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>70100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>16200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>17600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>112900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>112300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>109900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>59500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>57800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>61400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>67500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>70500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>74300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>50900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>57600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>59100</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,8 +3533,11 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3455,85 +3548,88 @@
         <v>1400</v>
       </c>
       <c r="F43" s="3">
-        <v>22500</v>
+        <v>1400</v>
       </c>
       <c r="G43" s="3">
+        <v>100</v>
+      </c>
+      <c r="H43" s="3">
         <v>1400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1700</v>
-      </c>
-      <c r="L43" s="3">
-        <v>1400</v>
       </c>
       <c r="M43" s="3">
         <v>1400</v>
       </c>
       <c r="N43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O43" s="3">
         <v>400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>400</v>
-      </c>
-      <c r="AD43" s="3">
-        <v>1000</v>
       </c>
       <c r="AE43" s="3">
         <v>1000</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3546,8 +3642,8 @@
       <c r="F44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>8</v>
+      <c r="G44" s="3">
+        <v>900</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>8</v>
@@ -3555,275 +3651,284 @@
       <c r="I44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J44" s="3">
+      <c r="J44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K44" s="3">
         <v>900</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N44" s="3">
+      <c r="N44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O44" s="3">
         <v>800</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R44" s="3">
+      <c r="R44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S44" s="3">
         <v>700</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U44" s="3">
+      <c r="U44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V44" s="3">
         <v>700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>800</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AC44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AD44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE44" s="3">
         <v>800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>39200</v>
+      </c>
+      <c r="E45" s="3">
         <v>45800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>32400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
+        <v>24700</v>
+      </c>
+      <c r="H45" s="3">
+        <v>40800</v>
+      </c>
+      <c r="I45" s="3">
+        <v>34500</v>
+      </c>
+      <c r="J45" s="3">
+        <v>29200</v>
+      </c>
+      <c r="K45" s="3">
+        <v>2600</v>
+      </c>
+      <c r="L45" s="3">
+        <v>6900</v>
+      </c>
+      <c r="M45" s="3">
+        <v>10700</v>
+      </c>
+      <c r="N45" s="3">
+        <v>6500</v>
+      </c>
+      <c r="O45" s="3">
+        <v>900</v>
+      </c>
+      <c r="P45" s="3">
+        <v>2500</v>
+      </c>
+      <c r="Q45" s="3">
         <v>3100</v>
       </c>
-      <c r="G45" s="3">
-        <v>40800</v>
-      </c>
-      <c r="H45" s="3">
-        <v>34500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>29200</v>
-      </c>
-      <c r="J45" s="3">
-        <v>2600</v>
-      </c>
-      <c r="K45" s="3">
-        <v>6900</v>
-      </c>
-      <c r="L45" s="3">
-        <v>10700</v>
-      </c>
-      <c r="M45" s="3">
-        <v>6500</v>
-      </c>
-      <c r="N45" s="3">
-        <v>900</v>
-      </c>
-      <c r="O45" s="3">
-        <v>2500</v>
-      </c>
-      <c r="P45" s="3">
-        <v>3100</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>302000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>32400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>105500</v>
+      </c>
+      <c r="E46" s="3">
         <v>100000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>86600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>74200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>139900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>138500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>138600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>51200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>99900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>98800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>91900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>27100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>79900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>69300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>75100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>18200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>322100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>118200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>114800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>113000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>63500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>65700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>66100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>70400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>74700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>77700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>83700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>60200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>62000</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>3100</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3888,97 +3993,103 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>805500</v>
+      </c>
+      <c r="E48" s="3">
         <v>809300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>817200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>825100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>833100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>838800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>845400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>853200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>861200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>869200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>877100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>884900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>892900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>900900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>908800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>916700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>924700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>932300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>939900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>947400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>955000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>962700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>970200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>977300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>984900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>992600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1000100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1007600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1015300</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4066,8 +4177,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,97 +4361,103 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E52" s="3">
         <v>10500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6900</v>
       </c>
-      <c r="F52" s="3">
-        <v>48400</v>
-      </c>
       <c r="G52" s="3">
+        <v>45200</v>
+      </c>
+      <c r="H52" s="3">
         <v>1300</v>
-      </c>
-      <c r="H52" s="3">
-        <v>1500</v>
       </c>
       <c r="I52" s="3">
         <v>1500</v>
       </c>
       <c r="J52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K52" s="3">
         <v>61100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>53800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>54300</v>
-      </c>
-      <c r="S52" s="3">
-        <v>3100</v>
       </c>
       <c r="T52" s="3">
         <v>3100</v>
       </c>
       <c r="U52" s="3">
+        <v>3100</v>
+      </c>
+      <c r="V52" s="3">
         <v>3300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>8400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>10300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>12100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>38900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>40700</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4545,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>916800</v>
+      </c>
+      <c r="E54" s="3">
         <v>919900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>910800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>947700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>974400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>978900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>985500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>965500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>962700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>969600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>971200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>965800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>975500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>973100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>986800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>989200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1249900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1053700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1058000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1063400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1021900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1032200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1041200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1054300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1068100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1080500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1095900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1106700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1117900</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,8 +4707,9 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4591,8 +4722,8 @@
       <c r="F57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>8</v>
+      <c r="G57" s="3">
+        <v>8000</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>8</v>
@@ -4600,74 +4731,77 @@
       <c r="I57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K57" s="3">
         <v>5700</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N57" s="3">
+      <c r="N57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O57" s="3">
         <v>4400</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R57" s="3">
+      <c r="R57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S57" s="3">
         <v>5500</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U57" s="3">
+      <c r="U57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V57" s="3">
         <v>5000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>6800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>7100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>9700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4680,8 +4814,8 @@
       <c r="F58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>8</v>
+      <c r="G58" s="3">
+        <v>46300</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>8</v>
@@ -4689,47 +4823,47 @@
       <c r="I58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J58" s="3">
+      <c r="J58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K58" s="3">
         <v>45900</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N58" s="3">
+      <c r="N58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O58" s="3">
         <v>45700</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R58" s="3">
+      <c r="R58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S58" s="3">
         <v>45500</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U58" s="3">
+      <c r="U58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V58" s="3">
         <v>252000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>251800</v>
-      </c>
-      <c r="W58" s="3">
-        <v>2700</v>
       </c>
       <c r="X58" s="3">
         <v>2700</v>
@@ -4741,327 +4875,339 @@
         <v>2700</v>
       </c>
       <c r="AA58" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="AB58" s="3">
         <v>2600</v>
       </c>
       <c r="AC58" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AD58" s="3">
         <v>3500</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>31700</v>
       </c>
       <c r="AE58" s="3">
         <v>31700</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>31700</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E59" s="3">
         <v>32300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>23200</v>
       </c>
-      <c r="F59" s="3">
-        <v>70300</v>
-      </c>
       <c r="G59" s="3">
+        <v>16000</v>
+      </c>
+      <c r="H59" s="3">
         <v>28800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>26300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>29500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>18700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>22600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>20900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>24500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>18100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>24000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>13700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>21300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>19800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>14500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>15300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>14300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>11700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>12500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>15700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>15600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>12700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>12400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>18300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E60" s="3">
         <v>32300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>23200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>70300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>28800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>26300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>29500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>64900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>18700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>22600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>20900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>62800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>24500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>18100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>24000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>64600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>21300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>19800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>271500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>272700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>23300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>23400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>21900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>22900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>25400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>25000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>20000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>53100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>55400</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>431200</v>
+      </c>
+      <c r="E61" s="3">
         <v>442800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>454400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>450800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>527500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>539000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>550500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>516000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>573400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>584800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>596300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>562000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>619100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>630400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>641800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>607700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>914400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>712000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>460400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>461100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>710500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>710900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>711300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>711700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>712100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>712300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>710900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>684700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>692400</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E62" s="3">
         <v>2600</v>
-      </c>
-      <c r="E62" s="3">
-        <v>2700</v>
       </c>
       <c r="F62" s="3">
         <v>2700</v>
       </c>
       <c r="G62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="H62" s="3">
         <v>2800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3000</v>
-      </c>
-      <c r="J62" s="3">
-        <v>3100</v>
       </c>
       <c r="K62" s="3">
         <v>3100</v>
       </c>
       <c r="L62" s="3">
-        <v>3200</v>
+        <v>3100</v>
       </c>
       <c r="M62" s="3">
         <v>3200</v>
       </c>
       <c r="N62" s="3">
+        <v>3200</v>
+      </c>
+      <c r="O62" s="3">
         <v>4500</v>
-      </c>
-      <c r="O62" s="3">
-        <v>3200</v>
       </c>
       <c r="P62" s="3">
         <v>3200</v>
@@ -5082,37 +5228,40 @@
         <v>3200</v>
       </c>
       <c r="V62" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="W62" s="3">
         <v>3100</v>
       </c>
       <c r="X62" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Y62" s="3">
         <v>1700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1100</v>
-      </c>
-      <c r="AC62" s="3">
-        <v>1000</v>
       </c>
       <c r="AD62" s="3">
         <v>1000</v>
       </c>
       <c r="AE62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AF62" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5533,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>476200</v>
+      </c>
+      <c r="E66" s="3">
         <v>477700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>480200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>523800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>559200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>568200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>583000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>584000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>595200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>610600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>620400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>629300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>646800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>651800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>669000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>675500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>938800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>735000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>735100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>737000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>736900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>736000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>734700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>736000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>738700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>738400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>731900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>738800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>748800</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5705,7 +5873,7 @@
         <v>126800</v>
       </c>
       <c r="K70" s="3">
-        <v>126700</v>
+        <v>126800</v>
       </c>
       <c r="L70" s="3">
         <v>126700</v>
@@ -5738,10 +5906,10 @@
         <v>126700</v>
       </c>
       <c r="V70" s="3">
+        <v>126700</v>
+      </c>
+      <c r="W70" s="3">
         <v>127100</v>
-      </c>
-      <c r="W70" s="3">
-        <v>73200</v>
       </c>
       <c r="X70" s="3">
         <v>73200</v>
@@ -5750,7 +5918,7 @@
         <v>73200</v>
       </c>
       <c r="Z70" s="3">
-        <v>73300</v>
+        <v>73200</v>
       </c>
       <c r="AA70" s="3">
         <v>73300</v>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>73300</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>73300</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,8 +6027,11 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5945,8 +6119,11 @@
       <c r="AE72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6395,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>313900</v>
+      </c>
+      <c r="E76" s="3">
         <v>315400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>303800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>297100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>288400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>283900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>275700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>254700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>240700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>232300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>224000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>209800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>202000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>194600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>191100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>187000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>184400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>192000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>196200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>199400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>211800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>223000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>233200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>245100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>256100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>268900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>290700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>294500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>295800</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,114 +6579,120 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E81" s="3">
         <v>14400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>9600</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G81" s="3" t="s">
         <v>8</v>
       </c>
@@ -6507,12 +6702,12 @@
       <c r="I81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J81" s="3">
+      <c r="J81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" s="3">
         <v>16900</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>8</v>
       </c>
@@ -6540,41 +6735,44 @@
       <c r="T81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V81" s="3">
         <v>-1000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>10000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>7900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6615,58 +6814,58 @@
         <v>8000</v>
       </c>
       <c r="E83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="F83" s="3">
         <v>7900</v>
-      </c>
-      <c r="F83" s="3">
-        <v>8000</v>
       </c>
       <c r="G83" s="3">
         <v>8000</v>
       </c>
       <c r="H83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="I83" s="3">
         <v>7900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7800</v>
-      </c>
-      <c r="J83" s="3">
-        <v>8000</v>
       </c>
       <c r="K83" s="3">
         <v>8000</v>
       </c>
       <c r="L83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="M83" s="3">
         <v>7900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7800</v>
-      </c>
-      <c r="N83" s="3">
-        <v>8000</v>
       </c>
       <c r="O83" s="3">
         <v>8000</v>
       </c>
       <c r="P83" s="3">
-        <v>7900</v>
+        <v>8000</v>
       </c>
       <c r="Q83" s="3">
         <v>7900</v>
       </c>
       <c r="R83" s="3">
+        <v>7900</v>
+      </c>
+      <c r="S83" s="3">
         <v>8000</v>
-      </c>
-      <c r="S83" s="3">
-        <v>7600</v>
       </c>
       <c r="T83" s="3">
         <v>7600</v>
       </c>
       <c r="U83" s="3">
+        <v>7600</v>
+      </c>
+      <c r="V83" s="3">
         <v>7500</v>
-      </c>
-      <c r="V83" s="3">
-        <v>7600</v>
       </c>
       <c r="W83" s="3">
         <v>7600</v>
@@ -6675,10 +6874,10 @@
         <v>7600</v>
       </c>
       <c r="Y83" s="3">
+        <v>7600</v>
+      </c>
+      <c r="Z83" s="3">
         <v>7500</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>7600</v>
       </c>
       <c r="AA83" s="3">
         <v>7600</v>
@@ -6687,16 +6886,19 @@
         <v>7600</v>
       </c>
       <c r="AC83" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AD83" s="3">
         <v>7500</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>7600</v>
       </c>
       <c r="AE83" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7354,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E89" s="3">
         <v>8800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>13700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>13400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>10900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>8200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>24800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>21000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>19800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>15800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>22900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>14200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>27600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>8100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>18700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>13500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>13600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>7000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>9200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>9000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>13500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>8600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>11900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>15000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>14800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>11400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>18200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>23300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>27000</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,40 +7482,41 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-1300</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>8</v>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>8</v>
@@ -7303,8 +7524,8 @@
       <c r="O91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -7318,17 +7539,17 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>8</v>
+      <c r="X91" s="3">
+        <v>0</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>8</v>
@@ -7342,17 +7563,20 @@
       <c r="AB91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
+      <c r="AC91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
       </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,32 +7756,35 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-1300</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>8</v>
       </c>
@@ -7564,8 +7794,8 @@
       <c r="M94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="N94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
@@ -7595,11 +7825,11 @@
         <v>0</v>
       </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-400</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
         <v>0</v>
       </c>
@@ -7616,10 +7846,13 @@
         <v>0</v>
       </c>
       <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7699,19 +7933,19 @@
         <v>0</v>
       </c>
       <c r="R96" s="3">
-        <v>-2900</v>
+        <v>0</v>
       </c>
       <c r="S96" s="3">
         <v>-2900</v>
       </c>
       <c r="T96" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="U96" s="3">
         <v>-5100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-5500</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-10600</v>
       </c>
       <c r="W96" s="3">
         <v>-10600</v>
@@ -7720,7 +7954,7 @@
         <v>-10600</v>
       </c>
       <c r="Y96" s="3">
-        <v>-16700</v>
+        <v>-10600</v>
       </c>
       <c r="Z96" s="3">
         <v>-16700</v>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>-16700</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>-16700</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,88 +8250,91 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-8800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-40600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-29200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-12400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-14100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-15200</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-15300</v>
       </c>
       <c r="K100" s="3">
         <v>-15300</v>
       </c>
       <c r="L100" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="M100" s="3">
         <v>-13100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-13800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-15200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-14800</v>
-      </c>
-      <c r="P100" s="3">
-        <v>-14900</v>
       </c>
       <c r="Q100" s="3">
         <v>-14900</v>
       </c>
       <c r="R100" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="S100" s="3">
         <v>-264900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>191200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-6300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-6800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>41400</v>
-      </c>
-      <c r="W100" s="3">
-        <v>-11800</v>
       </c>
       <c r="X100" s="3">
         <v>-11800</v>
       </c>
       <c r="Y100" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-17900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-18100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-18600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>12000</v>
-      </c>
-      <c r="AC100" s="3">
-        <v>-24800</v>
       </c>
       <c r="AD100" s="3">
         <v>-24800</v>
@@ -8096,8 +8342,11 @@
       <c r="AE100" s="3">
         <v>-24800</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3">
+        <v>-24800</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8185,93 +8434,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-27000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-17900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-6400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>9600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>4500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>9100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>12800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-251400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>204700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>50400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>23400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-6700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DLNG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DLNG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="92">
   <si>
     <t>DLNG</t>
   </si>
@@ -656,416 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E8" s="3">
         <v>48600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>37700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>37300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>35100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>29900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>33400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>33300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>35700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>34700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>33900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>33400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>34400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>34300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>33900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>34500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>34300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>34400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>30800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>31400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>31000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>31300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>30900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>33900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>34500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>33500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>32000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>39100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>41400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>43100</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E9" s="3">
         <v>11800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7900</v>
-      </c>
-      <c r="I9" s="3">
-        <v>8200</v>
       </c>
       <c r="J9" s="3">
         <v>8200</v>
       </c>
       <c r="K9" s="3">
+        <v>8200</v>
+      </c>
+      <c r="L9" s="3">
         <v>8700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>8300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>7800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>7600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>7800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8300</v>
-      </c>
-      <c r="U9" s="3">
-        <v>7500</v>
       </c>
       <c r="V9" s="3">
         <v>7500</v>
       </c>
       <c r="W9" s="3">
+        <v>7500</v>
+      </c>
+      <c r="X9" s="3">
         <v>7000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>7400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>6500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>7000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>7400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>6900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>7500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>7400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E10" s="3">
         <v>36800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>28800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>29300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>26600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>22000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>25200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>25100</v>
-      </c>
-      <c r="K10" s="3">
-        <v>27000</v>
       </c>
       <c r="L10" s="3">
         <v>27000</v>
       </c>
       <c r="M10" s="3">
+        <v>27000</v>
+      </c>
+      <c r="N10" s="3">
         <v>25600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>25800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>26600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>26400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>26300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>26000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>26500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>26100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>23300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>23900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>24000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>23900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>24400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>26900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>27100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>26600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>23200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>31600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>34000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>35600</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1298,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1294,14 +1313,14 @@
         <v>0</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-2100</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1317,8 +1336,8 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1374,70 +1393,73 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>8000</v>
+        <v>8100</v>
       </c>
       <c r="E15" s="3">
         <v>8000</v>
       </c>
       <c r="F15" s="3">
+        <v>8000</v>
+      </c>
+      <c r="G15" s="3">
         <v>7900</v>
-      </c>
-      <c r="G15" s="3">
-        <v>8000</v>
       </c>
       <c r="H15" s="3">
         <v>8000</v>
       </c>
       <c r="I15" s="3">
+        <v>8000</v>
+      </c>
+      <c r="J15" s="3">
         <v>7900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7800</v>
-      </c>
-      <c r="K15" s="3">
-        <v>8000</v>
       </c>
       <c r="L15" s="3">
         <v>8000</v>
       </c>
       <c r="M15" s="3">
+        <v>8000</v>
+      </c>
+      <c r="N15" s="3">
         <v>7900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>7800</v>
-      </c>
-      <c r="O15" s="3">
-        <v>8000</v>
       </c>
       <c r="P15" s="3">
         <v>8000</v>
       </c>
       <c r="Q15" s="3">
-        <v>7900</v>
+        <v>8000</v>
       </c>
       <c r="R15" s="3">
         <v>7900</v>
       </c>
       <c r="S15" s="3">
+        <v>7900</v>
+      </c>
+      <c r="T15" s="3">
         <v>8000</v>
-      </c>
-      <c r="T15" s="3">
-        <v>7600</v>
       </c>
       <c r="U15" s="3">
         <v>7600</v>
       </c>
       <c r="V15" s="3">
+        <v>7600</v>
+      </c>
+      <c r="W15" s="3">
         <v>7500</v>
-      </c>
-      <c r="W15" s="3">
-        <v>7600</v>
       </c>
       <c r="X15" s="3">
         <v>7600</v>
@@ -1446,10 +1468,10 @@
         <v>7600</v>
       </c>
       <c r="Z15" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AA15" s="3">
         <v>7500</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>7600</v>
       </c>
       <c r="AB15" s="3">
         <v>7600</v>
@@ -1458,16 +1480,19 @@
         <v>7600</v>
       </c>
       <c r="AD15" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AE15" s="3">
         <v>7500</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>7600</v>
       </c>
       <c r="AF15" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,23 +1522,24 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3">
         <v>39200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>19400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>18100</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1523,12 +1549,12 @@
       <c r="J17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="3">
         <v>18900</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1556,56 +1582,59 @@
       <c r="U17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V17" s="3">
+      <c r="V17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W17" s="3">
         <v>17000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>19300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>19400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>18300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>17100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>17000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>17600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>23200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>17200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>17100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3">
         <v>9400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>18300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>19200</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H18" s="3" t="s">
         <v>8</v>
       </c>
@@ -1615,12 +1644,12 @@
       <c r="J18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="3">
         <v>16800</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>8</v>
       </c>
@@ -1648,41 +1677,44 @@
       <c r="U18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W18" s="3">
         <v>14400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>11700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>11900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>12600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>16800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>17500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>15900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>8800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>21900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>24300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,23 +1747,24 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3">
         <v>-8000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-9600</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>8</v>
       </c>
@@ -1741,12 +1774,12 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>8</v>
       </c>
@@ -1774,56 +1807,59 @@
       <c r="U20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W20" s="3">
         <v>500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>300</v>
-      </c>
-      <c r="X20" s="3">
-        <v>200</v>
       </c>
       <c r="Y20" s="3">
         <v>200</v>
       </c>
       <c r="Z20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-100</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="3">
         <v>9400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>22400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>17500</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1833,12 +1869,12 @@
       <c r="J21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="3">
         <v>24900</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1866,41 +1902,44 @@
       <c r="U21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W21" s="3">
         <v>22400</v>
-      </c>
-      <c r="W21" s="3">
-        <v>19700</v>
       </c>
       <c r="X21" s="3">
         <v>19700</v>
       </c>
       <c r="Y21" s="3">
+        <v>19700</v>
+      </c>
+      <c r="Z21" s="3">
         <v>20400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>24300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>25100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>23400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>15100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>29200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>32000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>33600</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1940,8 +1979,8 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>8</v>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>8</v>
@@ -1958,56 +1997,59 @@
       <c r="U22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V22" s="3">
-        <v>13000</v>
+      <c r="V22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W22" s="3">
         <v>13000</v>
       </c>
       <c r="X22" s="3">
+        <v>13000</v>
+      </c>
+      <c r="Y22" s="3">
         <v>12700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>12500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>12000</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>11800</v>
       </c>
       <c r="AB22" s="3">
         <v>11800</v>
       </c>
       <c r="AC22" s="3">
+        <v>11800</v>
+      </c>
+      <c r="AD22" s="3">
         <v>12700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>8800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>8900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3">
         <v>1400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>14400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>9600</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H23" s="3" t="s">
         <v>8</v>
       </c>
@@ -2017,12 +2059,12 @@
       <c r="J23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="3">
         <v>16900</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>8</v>
       </c>
@@ -2050,41 +2092,44 @@
       <c r="U23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V23" s="3">
+      <c r="V23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W23" s="3">
         <v>1900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>5600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>12900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>15500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>17300</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2175,8 +2220,11 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,23 +2315,26 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3">
         <v>1400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>14400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>9600</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H26" s="3" t="s">
         <v>8</v>
       </c>
@@ -2293,12 +2344,12 @@
       <c r="J26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="3">
         <v>16900</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>8</v>
       </c>
@@ -2326,56 +2377,59 @@
       <c r="U26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V26" s="3">
+      <c r="V26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W26" s="3">
         <v>1900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>5600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>12900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>15500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>17300</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3">
         <v>1400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>14400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>9600</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H27" s="3" t="s">
         <v>8</v>
       </c>
@@ -2385,12 +2439,12 @@
       <c r="J27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="3">
         <v>16900</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>8</v>
       </c>
@@ -2418,41 +2472,44 @@
       <c r="U27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V27" s="3">
+      <c r="V27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W27" s="3">
         <v>-1000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>10000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>7900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,23 +2885,26 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3">
         <v>8000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>9600</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>8</v>
       </c>
@@ -2845,12 +2914,12 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>8</v>
       </c>
@@ -2878,56 +2947,59 @@
       <c r="U32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W32" s="3">
         <v>-500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-300</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-200</v>
       </c>
       <c r="Y32" s="3">
         <v>-200</v>
       </c>
       <c r="Z32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>100</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3">
         <v>1400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>14400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>9600</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H33" s="3" t="s">
         <v>8</v>
       </c>
@@ -2937,12 +3009,12 @@
       <c r="J33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L33" s="3">
         <v>16900</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>8</v>
       </c>
@@ -2970,41 +3042,44 @@
       <c r="U33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V33" s="3">
+      <c r="V33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W33" s="3">
         <v>-1000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>10000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>7900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,23 +3170,26 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3">
         <v>1400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>14400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>9600</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H35" s="3" t="s">
         <v>8</v>
       </c>
@@ -3121,12 +3199,12 @@
       <c r="J35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L35" s="3">
         <v>16900</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>8</v>
       </c>
@@ -3154,138 +3232,144 @@
       <c r="U35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V35" s="3">
+      <c r="V35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W35" s="3">
         <v>-1000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>10000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>7900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3437,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>73800</v>
+      </c>
+      <c r="E41" s="3">
         <v>64900</v>
-      </c>
-      <c r="E41" s="3">
-        <v>52900</v>
       </c>
       <c r="F41" s="3">
         <v>52900</v>
       </c>
       <c r="G41" s="3">
+        <v>52900</v>
+      </c>
+      <c r="H41" s="3">
         <v>48600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>97700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>100200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>106600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>47000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>91300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>86800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>84100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>25000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>76000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>63300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>70100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>16200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>17600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>112900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>112300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>109900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>59500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>57800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>61400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>67500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>70500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>74300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>50900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>57600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>59100</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,13 +3625,16 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="E43" s="3">
         <v>1400</v>
@@ -3551,90 +3643,93 @@
         <v>1400</v>
       </c>
       <c r="G43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1700</v>
-      </c>
-      <c r="M43" s="3">
-        <v>1400</v>
       </c>
       <c r="N43" s="3">
         <v>1400</v>
       </c>
       <c r="O43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P43" s="3">
         <v>400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>400</v>
-      </c>
-      <c r="AE43" s="3">
-        <v>1000</v>
       </c>
       <c r="AF43" s="3">
         <v>1000</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>8</v>
+      <c r="D44" s="3">
+        <v>800</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>8</v>
@@ -3642,275 +3737,284 @@
       <c r="F44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3">
         <v>900</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L44" s="3">
         <v>900</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
+      <c r="O44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P44" s="3">
         <v>800</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="R44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S44" s="3">
+      <c r="S44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T44" s="3">
         <v>700</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V44" s="3">
+      <c r="V44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W44" s="3">
         <v>700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>800</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AE44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF44" s="3">
         <v>800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E45" s="3">
         <v>39200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>45800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>32400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>24700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>40800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>34500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>29200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>302000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>32400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>105300</v>
+      </c>
+      <c r="E46" s="3">
         <v>105500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>100000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>86600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>74200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>139900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>138500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>138600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>51200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>99900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>98800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>91900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>27100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>79900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>69300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>75100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>18200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>322100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>118200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>114800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>113000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>63500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>65700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>66100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>70400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>74700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>77700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>83700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>60200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>62000</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>8</v>
+      <c r="D47" s="3">
+        <v>3100</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>8</v>
@@ -3918,20 +4022,20 @@
       <c r="F47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3">
         <v>3100</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3996,100 +4100,106 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>797400</v>
+      </c>
+      <c r="E48" s="3">
         <v>805500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>809300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>817200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>825100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>833100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>838800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>845400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>853200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>861200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>869200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>877100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>884900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>892900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>900900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>908800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>916700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>924700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>932300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>939900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>947400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>955000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>962700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>970200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>977300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>984900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>992600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1000100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1007600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1015300</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4180,8 +4290,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4480,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E52" s="3">
         <v>5900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>10500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>45200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1300</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1500</v>
       </c>
       <c r="J52" s="3">
         <v>1500</v>
       </c>
       <c r="K52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L52" s="3">
         <v>61100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>53800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>54300</v>
-      </c>
-      <c r="T52" s="3">
-        <v>3100</v>
       </c>
       <c r="U52" s="3">
         <v>3100</v>
       </c>
       <c r="V52" s="3">
+        <v>3100</v>
+      </c>
+      <c r="W52" s="3">
         <v>3300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>8400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>10300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>12100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>38900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>40700</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>908900</v>
+      </c>
+      <c r="E54" s="3">
         <v>916800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>919900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>910800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>947700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>974400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>978900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>985500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>965500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>962700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>969600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>971200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>965800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>975500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>973100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>986800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>989200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1249900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1053700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1058000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1063400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1021900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1032200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1041200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1054300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1068100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1080500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1095900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1106700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1117900</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,13 +4837,14 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>8</v>
+      <c r="D57" s="3">
+        <v>13800</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>8</v>
@@ -4722,91 +4852,94 @@
       <c r="F57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H57" s="3">
         <v>8000</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L57" s="3">
         <v>5700</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P57" s="3">
         <v>4400</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S57" s="3">
+      <c r="S57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T57" s="3">
         <v>5500</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V57" s="3">
+      <c r="V57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W57" s="3">
         <v>5000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>6300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>9100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>6800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>7100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>9700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>8</v>
+      <c r="D58" s="3">
+        <v>419600</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>8</v>
@@ -4814,59 +4947,59 @@
       <c r="F58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G58" s="3">
+      <c r="G58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H58" s="3">
         <v>46300</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K58" s="3">
+      <c r="K58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L58" s="3">
         <v>45900</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="3">
+      <c r="O58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P58" s="3">
         <v>45700</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S58" s="3">
+      <c r="S58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T58" s="3">
         <v>45500</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V58" s="3">
+      <c r="V58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W58" s="3">
         <v>252000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>251800</v>
-      </c>
-      <c r="X58" s="3">
-        <v>2700</v>
       </c>
       <c r="Y58" s="3">
         <v>2700</v>
@@ -4878,339 +5011,351 @@
         <v>2700</v>
       </c>
       <c r="AB58" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="AC58" s="3">
         <v>2600</v>
       </c>
       <c r="AD58" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AE58" s="3">
         <v>3500</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>31700</v>
       </c>
       <c r="AF58" s="3">
         <v>31700</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>31700</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E59" s="3">
         <v>42900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>32300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>23200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>28800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>26300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>29500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>18700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>22600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>20900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>24500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>18100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>24000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>21300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>19800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>14500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>15300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>14300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>11700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>12500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>15700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>15600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>12700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>12400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>18300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>458800</v>
+      </c>
+      <c r="E60" s="3">
         <v>42900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>32300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>23200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>70300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>28800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>26300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>29500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>64900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>18700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>22600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>20900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>62800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>24500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>18100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>24000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>64600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>21300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>19800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>271500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>272700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>23300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>23400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>21900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>22900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>25400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>25000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>20000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>53100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>55400</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>431200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>442800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>454400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>450800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>527500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>539000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>550500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>516000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>573400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>584800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>596300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>562000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>619100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>630400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>641800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>607700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>914400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>712000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>460400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>461100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>710500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>710900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>711300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>711700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>712100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>712300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>710900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>684700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>692400</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E62" s="3">
         <v>2100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2600</v>
-      </c>
-      <c r="F62" s="3">
-        <v>2700</v>
       </c>
       <c r="G62" s="3">
         <v>2700</v>
       </c>
       <c r="H62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I62" s="3">
         <v>2800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3000</v>
-      </c>
-      <c r="K62" s="3">
-        <v>3100</v>
       </c>
       <c r="L62" s="3">
         <v>3100</v>
       </c>
       <c r="M62" s="3">
-        <v>3200</v>
+        <v>3100</v>
       </c>
       <c r="N62" s="3">
         <v>3200</v>
       </c>
       <c r="O62" s="3">
+        <v>3200</v>
+      </c>
+      <c r="P62" s="3">
         <v>4500</v>
-      </c>
-      <c r="P62" s="3">
-        <v>3200</v>
       </c>
       <c r="Q62" s="3">
         <v>3200</v>
@@ -5231,37 +5376,40 @@
         <v>3200</v>
       </c>
       <c r="W62" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="X62" s="3">
         <v>3100</v>
       </c>
       <c r="Y62" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Z62" s="3">
         <v>1700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1100</v>
-      </c>
-      <c r="AD62" s="3">
-        <v>1000</v>
       </c>
       <c r="AE62" s="3">
         <v>1000</v>
       </c>
       <c r="AF62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AG62" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>460700</v>
+      </c>
+      <c r="E66" s="3">
         <v>476200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>477700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>480200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>523800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>559200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>568200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>583000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>584000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>595200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>610600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>620400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>629300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>646800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>651800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>669000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>675500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>938800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>735000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>735100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>737000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>736900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>736000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>734700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>736000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>738700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>738400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>731900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>738800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>748800</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5876,7 +6043,7 @@
         <v>126800</v>
       </c>
       <c r="L70" s="3">
-        <v>126700</v>
+        <v>126800</v>
       </c>
       <c r="M70" s="3">
         <v>126700</v>
@@ -5909,10 +6076,10 @@
         <v>126700</v>
       </c>
       <c r="W70" s="3">
+        <v>126700</v>
+      </c>
+      <c r="X70" s="3">
         <v>127100</v>
-      </c>
-      <c r="X70" s="3">
-        <v>73200</v>
       </c>
       <c r="Y70" s="3">
         <v>73200</v>
@@ -5921,7 +6088,7 @@
         <v>73200</v>
       </c>
       <c r="AA70" s="3">
-        <v>73300</v>
+        <v>73200</v>
       </c>
       <c r="AB70" s="3">
         <v>73300</v>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>73300</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>73300</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,8 +6200,11 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6122,8 +6295,11 @@
       <c r="AF72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>321400</v>
+      </c>
+      <c r="E76" s="3">
         <v>313900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>315400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>303800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>297100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>288400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>283900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>275700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>254700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>240700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>232300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>224000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>209800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>202000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>194600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>191100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>187000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>184400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>192000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>196200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>199400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>211800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>223000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>233200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>245100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>256100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>268900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>290700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>294500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>295800</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,120 +6770,126 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3">
         <v>1400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>14400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>9600</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H81" s="3" t="s">
         <v>8</v>
       </c>
@@ -6705,12 +6899,12 @@
       <c r="J81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L81" s="3">
         <v>16900</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>8</v>
       </c>
@@ -6738,41 +6932,44 @@
       <c r="U81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V81" s="3">
+      <c r="V81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W81" s="3">
         <v>-1000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>10000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>7900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,70 +7002,71 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>8000</v>
+        <v>8100</v>
       </c>
       <c r="E83" s="3">
         <v>8000</v>
       </c>
       <c r="F83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="G83" s="3">
         <v>7900</v>
-      </c>
-      <c r="G83" s="3">
-        <v>8000</v>
       </c>
       <c r="H83" s="3">
         <v>8000</v>
       </c>
       <c r="I83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="J83" s="3">
         <v>7900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7800</v>
-      </c>
-      <c r="K83" s="3">
-        <v>8000</v>
       </c>
       <c r="L83" s="3">
         <v>8000</v>
       </c>
       <c r="M83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="N83" s="3">
         <v>7900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7800</v>
-      </c>
-      <c r="O83" s="3">
-        <v>8000</v>
       </c>
       <c r="P83" s="3">
         <v>8000</v>
       </c>
       <c r="Q83" s="3">
-        <v>7900</v>
+        <v>8000</v>
       </c>
       <c r="R83" s="3">
         <v>7900</v>
       </c>
       <c r="S83" s="3">
+        <v>7900</v>
+      </c>
+      <c r="T83" s="3">
         <v>8000</v>
-      </c>
-      <c r="T83" s="3">
-        <v>7600</v>
       </c>
       <c r="U83" s="3">
         <v>7600</v>
       </c>
       <c r="V83" s="3">
+        <v>7600</v>
+      </c>
+      <c r="W83" s="3">
         <v>7500</v>
-      </c>
-      <c r="W83" s="3">
-        <v>7600</v>
       </c>
       <c r="X83" s="3">
         <v>7600</v>
@@ -6877,10 +7075,10 @@
         <v>7600</v>
       </c>
       <c r="Z83" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AA83" s="3">
         <v>7500</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>7600</v>
       </c>
       <c r="AB83" s="3">
         <v>7600</v>
@@ -6889,16 +7087,19 @@
         <v>7600</v>
       </c>
       <c r="AD83" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AE83" s="3">
         <v>7500</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>7600</v>
       </c>
       <c r="AF83" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E89" s="3">
         <v>21800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>8800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>13700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>13400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>10900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>8200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>24800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>21000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>19800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>15800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>22900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>14200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>27600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>8100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>18700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>13500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>13600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>7000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>9200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>9000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>13500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>8600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>11900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>15000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>14800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>11400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>18200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>23300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>27000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,43 +7702,44 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1300</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>8</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>8</v>
@@ -7527,8 +7747,8 @@
       <c r="P91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -7542,17 +7762,17 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>8</v>
+      <c r="Y91" s="3">
+        <v>0</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>8</v>
@@ -7566,17 +7786,20 @@
       <c r="AC91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
+      <c r="AD91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE91" s="3">
         <v>0</v>
       </c>
       <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,35 +7985,38 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1300</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>8</v>
       </c>
@@ -7797,8 +8026,8 @@
       <c r="N94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
@@ -7828,11 +8057,11 @@
         <v>0</v>
       </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-400</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
       <c r="AA94" s="3">
         <v>0</v>
       </c>
@@ -7849,10 +8078,13 @@
         <v>0</v>
       </c>
       <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7936,19 +8169,19 @@
         <v>0</v>
       </c>
       <c r="S96" s="3">
-        <v>-2900</v>
+        <v>0</v>
       </c>
       <c r="T96" s="3">
         <v>-2900</v>
       </c>
       <c r="U96" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="V96" s="3">
         <v>-5100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-5500</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-10600</v>
       </c>
       <c r="X96" s="3">
         <v>-10600</v>
@@ -7957,7 +8190,7 @@
         <v>-10600</v>
       </c>
       <c r="Z96" s="3">
-        <v>-16700</v>
+        <v>-10600</v>
       </c>
       <c r="AA96" s="3">
         <v>-16700</v>
@@ -7977,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>-16700</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>-16700</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,91 +8495,94 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-8400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-8800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-40600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-29200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-12400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-14100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-15200</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-15300</v>
       </c>
       <c r="L100" s="3">
         <v>-15300</v>
       </c>
       <c r="M100" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="N100" s="3">
         <v>-13100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-13800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-15200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-14800</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>-14900</v>
       </c>
       <c r="R100" s="3">
         <v>-14900</v>
       </c>
       <c r="S100" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="T100" s="3">
         <v>-264900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>191200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-6300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-6800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>41400</v>
-      </c>
-      <c r="X100" s="3">
-        <v>-11800</v>
       </c>
       <c r="Y100" s="3">
         <v>-11800</v>
       </c>
       <c r="Z100" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-17900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-18100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-18600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>12000</v>
-      </c>
-      <c r="AD100" s="3">
-        <v>-24800</v>
       </c>
       <c r="AE100" s="3">
         <v>-24800</v>
@@ -8345,8 +8590,11 @@
       <c r="AF100" s="3">
         <v>-24800</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>-24800</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,96 +8685,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E102" s="3">
         <v>12000</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-27000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-17900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>9600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>9100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>12800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-251400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>204700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>50400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>23400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-6700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DLNG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DLNG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="92">
   <si>
     <t>DLNG</t>
   </si>
@@ -656,428 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>37600</v>
+      </c>
+      <c r="E8" s="3">
+        <v>38100</v>
+      </c>
+      <c r="F8" s="3">
         <v>37000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>48600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>37700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>37300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>35100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>29900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>33400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>33300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>35700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>34700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>33900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>33400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>34400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>34300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>33900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>34500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>34300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>34400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>30800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>31400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>31000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>31300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>30900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>33900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>34500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>33500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>32000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>39100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>41400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>43100</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>8600</v>
+      </c>
+      <c r="F9" s="3">
         <v>9000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>11800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>8900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>8000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>8500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>7900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>8200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>8200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>8700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>7700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>8300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>7600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>7800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>7900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>7600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>8500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>7800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>8300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>7500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>7500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>7000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>7400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>6500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>7000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>7400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>6900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>8800</v>
-      </c>
-      <c r="AE9" s="3">
-        <v>7500</v>
-      </c>
-      <c r="AF9" s="3">
-        <v>7400</v>
       </c>
       <c r="AG9" s="3">
         <v>7500</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3">
+        <v>7400</v>
+      </c>
+      <c r="AI9" s="3">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>29500</v>
+      </c>
+      <c r="F10" s="3">
         <v>28000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>36800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>28800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>29300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>26600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>22000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>25200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>25100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>27000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>27000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>25600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>25800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>26600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>26400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>26300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>26000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>26500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>26100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>23300</v>
-      </c>
-      <c r="W10" s="3">
-        <v>23900</v>
-      </c>
-      <c r="X10" s="3">
-        <v>24000</v>
       </c>
       <c r="Y10" s="3">
         <v>23900</v>
       </c>
       <c r="Z10" s="3">
+        <v>24000</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>23900</v>
+      </c>
+      <c r="AB10" s="3">
         <v>24400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>26900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>27100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>26600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>23200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>31600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>34000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>35600</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,8 +1137,10 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1206,8 +1234,14 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,13 +1335,19 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1316,17 +1356,17 @@
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>-2100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1339,11 +1379,11 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1396,103 +1436,115 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>8100</v>
+        <v>8000</v>
       </c>
       <c r="E15" s="3">
         <v>8000</v>
       </c>
       <c r="F15" s="3">
+        <v>8100</v>
+      </c>
+      <c r="G15" s="3">
         <v>8000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>7900</v>
       </c>
       <c r="H15" s="3">
         <v>8000</v>
       </c>
       <c r="I15" s="3">
+        <v>7900</v>
+      </c>
+      <c r="J15" s="3">
         <v>8000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
+        <v>8000</v>
+      </c>
+      <c r="L15" s="3">
         <v>7900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>7800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>8000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>8000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>7900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>7800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>8000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>8000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>7900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>7900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>8000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>7600</v>
-      </c>
-      <c r="V15" s="3">
-        <v>7600</v>
-      </c>
-      <c r="W15" s="3">
-        <v>7500</v>
       </c>
       <c r="X15" s="3">
         <v>7600</v>
       </c>
       <c r="Y15" s="3">
-        <v>7600</v>
+        <v>7500</v>
       </c>
       <c r="Z15" s="3">
         <v>7600</v>
       </c>
       <c r="AA15" s="3">
-        <v>7500</v>
+        <v>7600</v>
       </c>
       <c r="AB15" s="3">
         <v>7600</v>
       </c>
       <c r="AC15" s="3">
-        <v>7600</v>
+        <v>7500</v>
       </c>
       <c r="AD15" s="3">
         <v>7600</v>
       </c>
       <c r="AE15" s="3">
-        <v>7500</v>
+        <v>7600</v>
       </c>
       <c r="AF15" s="3">
         <v>7600</v>
       </c>
       <c r="AG15" s="3">
+        <v>7500</v>
+      </c>
+      <c r="AH15" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,44 +1575,46 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>8</v>
+      <c r="D17" s="3">
+        <v>19100</v>
       </c>
       <c r="E17" s="3">
-        <v>39200</v>
-      </c>
-      <c r="F17" s="3">
+        <v>18700</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="3">
         <v>19400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>18100</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J17" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="3">
         <v>18900</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1585,77 +1639,83 @@
       <c r="V17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y17" s="3">
         <v>17000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>19300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>19400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>18300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>17100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>17000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>17600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>23200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>17200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>17100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>8</v>
+      <c r="D18" s="3">
+        <v>18500</v>
       </c>
       <c r="E18" s="3">
-        <v>9400</v>
-      </c>
-      <c r="F18" s="3">
+        <v>19400</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="3">
         <v>18300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>19200</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="3">
         <v>16800</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>8</v>
       </c>
@@ -1680,41 +1740,47 @@
       <c r="V18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y18" s="3">
         <v>14400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>11700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>11900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>12600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>16800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>17500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>15900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>8800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>21900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>24300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,44 +1814,46 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>-7800</v>
       </c>
       <c r="E20" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="F20" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3">
         <v>-3900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-9600</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
@@ -1810,77 +1878,83 @@
       <c r="V20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y20" s="3">
         <v>500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>200</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-1200</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>0</v>
       </c>
       <c r="AG20" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>18700</v>
       </c>
       <c r="E21" s="3">
-        <v>9400</v>
-      </c>
-      <c r="F21" s="3">
+        <v>19700</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="3">
         <v>22400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>17500</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="3">
         <v>24900</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1905,41 +1979,47 @@
       <c r="V21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y21" s="3">
         <v>22400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>19700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>19700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>20400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>24300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>25100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>23400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>15100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>29200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>32000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>33600</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1982,11 +2062,11 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>8</v>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>8</v>
@@ -2000,77 +2080,83 @@
       <c r="V22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y22" s="3">
         <v>13000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>13000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>12700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>12500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>12000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>11800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>11800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>12700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>8800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>8900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>8</v>
+      <c r="D23" s="3">
+        <v>10700</v>
       </c>
       <c r="E23" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3">
         <v>1400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>14400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>9600</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J23" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="3">
         <v>16900</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>8</v>
       </c>
@@ -2095,41 +2181,47 @@
       <c r="V23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W23" s="3">
+      <c r="W23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y23" s="3">
         <v>1900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>4800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>5600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>4000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-5200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>12900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>15500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>17300</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2223,8 +2315,14 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,44 +2416,50 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>8</v>
+      <c r="D26" s="3">
+        <v>10700</v>
       </c>
       <c r="E26" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F26" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="3">
         <v>14400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>9600</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J26" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N26" s="3">
         <v>16900</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>8</v>
       </c>
@@ -2380,77 +2484,83 @@
       <c r="V26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y26" s="3">
         <v>1900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>4800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>5600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>4000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-5200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>12900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>15500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>17300</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>8</v>
+      <c r="D27" s="3">
+        <v>10700</v>
       </c>
       <c r="E27" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F27" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="3">
         <v>14400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>9600</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J27" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N27" s="3">
         <v>16900</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>8</v>
       </c>
@@ -2475,41 +2585,47 @@
       <c r="V27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-1000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>3100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>3900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>2300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-6900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>10000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>7900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2719,14 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2698,8 +2820,14 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2921,14 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,44 +3022,50 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>7800</v>
       </c>
       <c r="E32" s="3">
-        <v>8000</v>
-      </c>
-      <c r="F32" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3">
         <v>3900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>9600</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
@@ -2950,77 +3090,83 @@
       <c r="V32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-200</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>1200</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>0</v>
       </c>
       <c r="AG32" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>8</v>
+      <c r="D33" s="3">
+        <v>10700</v>
       </c>
       <c r="E33" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F33" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" s="3">
         <v>14400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>9600</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J33" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N33" s="3">
         <v>16900</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>8</v>
       </c>
@@ -3045,41 +3191,47 @@
       <c r="V33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-1000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>3100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>3900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>2300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-6900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>10000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>7900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,44 +3325,50 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>8</v>
+      <c r="D35" s="3">
+        <v>10700</v>
       </c>
       <c r="E35" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F35" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" s="3">
         <v>14400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>9600</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J35" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N35" s="3">
         <v>16900</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>8</v>
       </c>
@@ -3235,141 +3393,153 @@
       <c r="V35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-1000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>3100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>3900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>2300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-6900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>10000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>7900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3573,10 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,103 +3610,111 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>35600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>76200</v>
+      </c>
+      <c r="F41" s="3">
         <v>73800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>64900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>52900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>52900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>48600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>97700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>100200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>106600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>47000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>91300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>86800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>84100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>25000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>76000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>63300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>70100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>16200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>17600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>112900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>112300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>109900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>59500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>57800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>61400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>67500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>70500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>74300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>50900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>57600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>59100</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3628,420 +3808,450 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>700</v>
+        <v>2300</v>
       </c>
       <c r="E43" s="3">
         <v>1400</v>
       </c>
       <c r="F43" s="3">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="G43" s="3">
         <v>1400</v>
       </c>
       <c r="H43" s="3">
-        <v>100</v>
+        <v>1400</v>
       </c>
       <c r="I43" s="3">
         <v>1400</v>
       </c>
       <c r="J43" s="3">
+        <v>100</v>
+      </c>
+      <c r="K43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L43" s="3">
         <v>3800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1400</v>
-      </c>
-      <c r="O43" s="3">
-        <v>1400</v>
-      </c>
-      <c r="P43" s="3">
-        <v>400</v>
       </c>
       <c r="Q43" s="3">
         <v>1400</v>
       </c>
       <c r="R43" s="3">
-        <v>2900</v>
+        <v>400</v>
       </c>
       <c r="S43" s="3">
         <v>1400</v>
       </c>
       <c r="T43" s="3">
+        <v>2900</v>
+      </c>
+      <c r="U43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="V43" s="3">
         <v>100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>2500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>1100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>1200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>2400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>1700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>1000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>1000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3">
         <v>800</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3">
         <v>900</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N44" s="3">
         <v>900</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P44" s="3">
+      <c r="P44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R44" s="3">
         <v>800</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T44" s="3">
+      <c r="T44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V44" s="3">
         <v>700</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W44" s="3">
+      <c r="W44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y44" s="3">
         <v>700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>1200</v>
-      </c>
-      <c r="Y44" s="3">
-        <v>1800</v>
-      </c>
-      <c r="Z44" s="3">
-        <v>3900</v>
       </c>
       <c r="AA44" s="3">
         <v>1800</v>
       </c>
       <c r="AB44" s="3">
+        <v>3900</v>
+      </c>
+      <c r="AC44" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AD44" s="3">
         <v>800</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AF44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH44" s="3">
         <v>800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>22700</v>
+      </c>
+      <c r="F45" s="3">
         <v>30000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>39200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>45800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>32400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>24700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>40800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>34500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>29200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>2600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>6900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>10700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>6500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>2500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>3100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>3700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>302000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>3400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>1000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>1200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>1100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>3700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>2700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>32400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>100300</v>
+      </c>
+      <c r="F46" s="3">
         <v>105300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>105500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>100000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>86600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>74200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>139900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>138500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>138600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>51200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>99900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>98800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>91900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>27100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>79900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>69300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>75100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>18200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>322100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>118200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>114800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>113000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>63500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>65700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>66100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>70400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>74700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>77700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>83700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>60200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>62000</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3">
         <v>3100</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3">
         <v>3100</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4103,103 +4313,115 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>781400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>789400</v>
+      </c>
+      <c r="F48" s="3">
         <v>797400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>805500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>809300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>817200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>825100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>833100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>838800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>845400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>853200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>861200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>869200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>877100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>884900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>892900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>900900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>908800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>916700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>924700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>932300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>939900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>947400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>955000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>962700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>970200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>977300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>984900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>992600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>1000100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>1007600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>1015300</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4293,8 +4515,14 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4616,14 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,103 +4717,115 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F52" s="3">
         <v>3200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>5900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>10500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>6900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>45200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>61100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>2200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>53800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>2700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>3000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>2900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>54300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>3100</v>
-      </c>
-      <c r="V52" s="3">
-        <v>3100</v>
-      </c>
-      <c r="W52" s="3">
-        <v>3300</v>
       </c>
       <c r="X52" s="3">
         <v>3100</v>
       </c>
       <c r="Y52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="Z52" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AA52" s="3">
         <v>3400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>3800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>4800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>6600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>8400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>10300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>12100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>38900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>40700</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4919,115 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>838400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>894800</v>
+      </c>
+      <c r="F54" s="3">
         <v>908900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>916800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>919900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>910800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>947700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>974400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>978900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>985500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>965500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>962700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>969600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>971200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>965800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>975500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>973100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>986800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>989200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1249900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1053700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1058000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1063400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1021900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1032200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1041200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1054300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1068100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1080500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1095900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>1106700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>1117900</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +5061,10 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,174 +5098,182 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="3">
         <v>13800</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J57" s="3">
         <v>8000</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N57" s="3">
         <v>5700</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R57" s="3">
         <v>4400</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T57" s="3">
+      <c r="T57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V57" s="3">
         <v>5500</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W57" s="3">
+      <c r="W57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y57" s="3">
         <v>5000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>5700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>6300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>9100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>6800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>4500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>7100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>9700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>4100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>3100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" s="3">
         <v>419600</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J58" s="3">
         <v>46300</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L58" s="3">
+      <c r="L58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N58" s="3">
         <v>45900</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P58" s="3">
+      <c r="P58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R58" s="3">
         <v>45700</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T58" s="3">
+      <c r="T58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V58" s="3">
         <v>45500</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W58" s="3">
+      <c r="W58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y58" s="3">
         <v>252000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>251800</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>2700</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>2700</v>
       </c>
       <c r="AA58" s="3">
         <v>2700</v>
@@ -5014,354 +5282,378 @@
         <v>2700</v>
       </c>
       <c r="AC58" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AD58" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AE58" s="3">
         <v>2600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>2600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>3500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>31700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>31700</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>27200</v>
+      </c>
+      <c r="F59" s="3">
         <v>25400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>42900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>32300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>23200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>16000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>28800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>26300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>29500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>13300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>18700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>22600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>20900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>12800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>24500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>18100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>24000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>13700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>21300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>19800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>14500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>15300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>14300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>11700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>12500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>15700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>15600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>12700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>12400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>18300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>27200</v>
+      </c>
+      <c r="F60" s="3">
         <v>458800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>42900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>32300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>23200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>70300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>28800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>26300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>29500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>64900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>18700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>22600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>20900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>62800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>24500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>18100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>24000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>64600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>21300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>19800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>271500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>272700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>23300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>23400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>21900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>22900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>25400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>25000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>20000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>53100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>55400</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>342500</v>
       </c>
       <c r="E61" s="3">
+        <v>408000</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>431200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>442800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>454400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>450800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>527500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>539000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>550500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>516000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>573400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>584800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>596300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>562000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>619100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>630400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>641800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>607700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>914400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>712000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>460400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>461100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>710500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>710900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>711300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>711700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>712100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>712300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>710900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>684700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>692400</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>31300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F62" s="3">
         <v>1900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>2100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>2600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>2700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>2700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>2800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>2900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>3000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>3100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>3100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>3200</v>
-      </c>
-      <c r="O62" s="3">
-        <v>3200</v>
-      </c>
-      <c r="P62" s="3">
-        <v>4500</v>
       </c>
       <c r="Q62" s="3">
         <v>3200</v>
       </c>
       <c r="R62" s="3">
-        <v>3200</v>
+        <v>4500</v>
       </c>
       <c r="S62" s="3">
         <v>3200</v>
@@ -5379,37 +5671,43 @@
         <v>3200</v>
       </c>
       <c r="X62" s="3">
+        <v>3200</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>3200</v>
+      </c>
+      <c r="Z62" s="3">
         <v>3100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>3100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>1700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>1500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>1400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>1300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>1100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>1000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>1000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5801,14 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5902,14 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +6003,115 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>374200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>438100</v>
+      </c>
+      <c r="F66" s="3">
         <v>460700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>476200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>477700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>480200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>523800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>559200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>568200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>583000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>584000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>595200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>610600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>620400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>629300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>646800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>651800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>669000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>675500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>938800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>735000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>735100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>737000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>736900</v>
-      </c>
-      <c r="Z66" s="3">
-        <v>736000</v>
-      </c>
-      <c r="AA66" s="3">
-        <v>734700</v>
       </c>
       <c r="AB66" s="3">
         <v>736000</v>
       </c>
       <c r="AC66" s="3">
+        <v>734700</v>
+      </c>
+      <c r="AD66" s="3">
+        <v>736000</v>
+      </c>
+      <c r="AE66" s="3">
         <v>738700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>738400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>731900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>738800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>748800</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +6145,10 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6242,14 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6343,14 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6046,10 +6382,10 @@
         <v>126800</v>
       </c>
       <c r="M70" s="3">
-        <v>126700</v>
+        <v>126800</v>
       </c>
       <c r="N70" s="3">
-        <v>126700</v>
+        <v>126800</v>
       </c>
       <c r="O70" s="3">
         <v>126700</v>
@@ -6079,22 +6415,22 @@
         <v>126700</v>
       </c>
       <c r="X70" s="3">
+        <v>126700</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>126700</v>
+      </c>
+      <c r="Z70" s="3">
         <v>127100</v>
-      </c>
-      <c r="Y70" s="3">
-        <v>73200</v>
-      </c>
-      <c r="Z70" s="3">
-        <v>73200</v>
       </c>
       <c r="AA70" s="3">
         <v>73200</v>
       </c>
       <c r="AB70" s="3">
-        <v>73300</v>
+        <v>73200</v>
       </c>
       <c r="AC70" s="3">
-        <v>73300</v>
+        <v>73200</v>
       </c>
       <c r="AD70" s="3">
         <v>73300</v>
@@ -6108,8 +6444,14 @@
       <c r="AG70" s="3">
         <v>73300</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>73300</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>73300</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,8 +6545,14 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6298,8 +6646,14 @@
       <c r="AG72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6747,14 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6848,14 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6949,115 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>337400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>329900</v>
+      </c>
+      <c r="F76" s="3">
         <v>321400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>313900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>315400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>303800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>297100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>288400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>283900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>275700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>254700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>240700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>232300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>224000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>209800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>202000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>194600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>191100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>187000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>184400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>192000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>196200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>199400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>211800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>223000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>233200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>245100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>256100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>268900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>290700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>294500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>295800</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,144 +7151,156 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>8</v>
+      <c r="D81" s="3">
+        <v>10700</v>
       </c>
       <c r="E81" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F81" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H81" s="3">
         <v>14400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>9600</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J81" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N81" s="3">
         <v>16900</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>8</v>
       </c>
@@ -6935,41 +7325,47 @@
       <c r="V81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-1000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>3100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>3900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>2300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-6900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>10000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>7900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,103 +7399,111 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>8100</v>
+        <v>8000</v>
       </c>
       <c r="E83" s="3">
         <v>8000</v>
       </c>
       <c r="F83" s="3">
+        <v>8100</v>
+      </c>
+      <c r="G83" s="3">
         <v>8000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>7900</v>
       </c>
       <c r="H83" s="3">
         <v>8000</v>
       </c>
       <c r="I83" s="3">
+        <v>7900</v>
+      </c>
+      <c r="J83" s="3">
         <v>8000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="L83" s="3">
         <v>7900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>7800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>8000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>8000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>7900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>7800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>8000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>8000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>7900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>7900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>8000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>7600</v>
-      </c>
-      <c r="V83" s="3">
-        <v>7600</v>
-      </c>
-      <c r="W83" s="3">
-        <v>7500</v>
       </c>
       <c r="X83" s="3">
         <v>7600</v>
       </c>
       <c r="Y83" s="3">
-        <v>7600</v>
+        <v>7500</v>
       </c>
       <c r="Z83" s="3">
         <v>7600</v>
       </c>
       <c r="AA83" s="3">
-        <v>7500</v>
+        <v>7600</v>
       </c>
       <c r="AB83" s="3">
         <v>7600</v>
       </c>
       <c r="AC83" s="3">
-        <v>7600</v>
+        <v>7500</v>
       </c>
       <c r="AD83" s="3">
         <v>7600</v>
       </c>
       <c r="AE83" s="3">
-        <v>7500</v>
+        <v>7600</v>
       </c>
       <c r="AF83" s="3">
         <v>7600</v>
       </c>
       <c r="AG83" s="3">
+        <v>7500</v>
+      </c>
+      <c r="AH83" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7597,14 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7698,14 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7799,14 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7900,14 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +8001,115 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>11600</v>
+      </c>
+      <c r="F89" s="3">
         <v>20200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>21800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>8800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>13700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>13400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>10900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>8200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>24800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>21000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>19800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>15800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>22900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>14200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>27600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>8100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>18700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>13500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>13600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>7000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>9200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>9000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>13500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>8600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>11900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>15000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>14800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>11400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>18200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>23300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>27000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,58 +8143,60 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-2800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1300</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-2000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>8</v>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="R91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
@@ -7765,20 +8207,20 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>8</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA91" s="3" t="s">
-        <v>8</v>
+      <c r="Y91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>0</v>
       </c>
       <c r="AB91" s="3" t="s">
         <v>8</v>
@@ -7789,17 +8231,23 @@
       <c r="AD91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>0</v>
+      <c r="AE91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8341,14 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,52 +8442,58 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-2800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1300</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-2000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="P94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
@@ -8060,14 +8520,14 @@
         <v>0</v>
       </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-400</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
       <c r="AC94" s="3">
         <v>0</v>
       </c>
@@ -8081,10 +8541,16 @@
         <v>0</v>
       </c>
       <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8584,10 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8172,31 +8640,31 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-2900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-2900</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-5100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-5500</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-10600</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-10600</v>
       </c>
       <c r="Z96" s="3">
         <v>-10600</v>
       </c>
       <c r="AA96" s="3">
-        <v>-16700</v>
+        <v>-10600</v>
       </c>
       <c r="AB96" s="3">
-        <v>-16700</v>
+        <v>-10600</v>
       </c>
       <c r="AC96" s="3">
         <v>-16700</v>
@@ -8213,8 +8681,14 @@
       <c r="AG96" s="3">
         <v>-16700</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>-16700</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8782,14 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8883,14 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,103 +8984,115 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-63100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="F100" s="3">
         <v>-8500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-8400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-8800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-40600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-29200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-12400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-14100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-15200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-15300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-15300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-13100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-13800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-14800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-14900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-14900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-264900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>191200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-6300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-6800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>41400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-11800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-11800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-17900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-18100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-18600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>12000</v>
-      </c>
-      <c r="AE100" s="3">
-        <v>-24800</v>
-      </c>
-      <c r="AF100" s="3">
-        <v>-24800</v>
       </c>
       <c r="AG100" s="3">
         <v>-24800</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="AI100" s="3">
+        <v>-24800</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8688,99 +9186,111 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-40600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F102" s="3">
         <v>8800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>12000</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-27000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-17900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-2500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-6400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>9600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>5700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>4500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>2700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>9100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>12800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-6800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>3800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-251400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>204700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>2400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>50400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>1700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-6100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>23400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-6700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>1800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DLNG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DLNG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="92">
   <si>
     <t>DLNG</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E8" s="3">
         <v>37600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>38100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>37000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>48600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>37700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>37300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>35100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>29900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>33400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>33300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>35700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>34700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>33900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>33400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>34400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>34300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>33900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>34500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>34300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>34400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>30800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>31400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>31000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>31300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>30900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>33900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>34500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>33500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>32000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>39100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>41400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>43100</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>8600</v>
+        <v>8900</v>
       </c>
       <c r="E9" s="3">
         <v>8600</v>
       </c>
       <c r="F9" s="3">
+        <v>8600</v>
+      </c>
+      <c r="G9" s="3">
         <v>9000</v>
       </c>
-      <c r="G9" s="3">
-        <v>11800</v>
-      </c>
       <c r="H9" s="3">
-        <v>8900</v>
+        <v>29100</v>
       </c>
       <c r="I9" s="3">
+        <v>9300</v>
+      </c>
+      <c r="J9" s="3">
         <v>8000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7900</v>
-      </c>
-      <c r="L9" s="3">
-        <v>8200</v>
       </c>
       <c r="M9" s="3">
         <v>8200</v>
       </c>
       <c r="N9" s="3">
+        <v>8200</v>
+      </c>
+      <c r="O9" s="3">
         <v>8700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>7700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>7600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>7800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>7900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>7600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>7800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8300</v>
-      </c>
-      <c r="X9" s="3">
-        <v>7500</v>
       </c>
       <c r="Y9" s="3">
         <v>7500</v>
       </c>
       <c r="Z9" s="3">
+        <v>7500</v>
+      </c>
+      <c r="AA9" s="3">
         <v>7000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>7400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>6500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>7000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>7400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>6900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>7500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>7400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E10" s="3">
         <v>29000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>29500</v>
       </c>
-      <c r="F10" s="3">
-        <v>28000</v>
-      </c>
       <c r="G10" s="3">
-        <v>36800</v>
+        <v>27900</v>
       </c>
       <c r="H10" s="3">
-        <v>28800</v>
+        <v>19500</v>
       </c>
       <c r="I10" s="3">
+        <v>28400</v>
+      </c>
+      <c r="J10" s="3">
         <v>29300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>26600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>22000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>25200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>25100</v>
-      </c>
-      <c r="N10" s="3">
-        <v>27000</v>
       </c>
       <c r="O10" s="3">
         <v>27000</v>
       </c>
       <c r="P10" s="3">
+        <v>27000</v>
+      </c>
+      <c r="Q10" s="3">
         <v>25600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>25800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>26600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>26400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>26300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>26000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>26500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>26100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>23300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>23900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>24000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>23900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>24400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>26900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>27100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>26600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>23200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>31600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>34000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>35600</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,35 +1358,38 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+        <v>-2900</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-2100</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1385,8 +1405,8 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1442,79 +1462,82 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>8000</v>
+        <v>8100</v>
       </c>
       <c r="E15" s="3">
         <v>8000</v>
       </c>
       <c r="F15" s="3">
+        <v>8000</v>
+      </c>
+      <c r="G15" s="3">
         <v>8100</v>
-      </c>
-      <c r="G15" s="3">
-        <v>8000</v>
       </c>
       <c r="H15" s="3">
         <v>8000</v>
       </c>
       <c r="I15" s="3">
+        <v>8000</v>
+      </c>
+      <c r="J15" s="3">
         <v>7900</v>
-      </c>
-      <c r="J15" s="3">
-        <v>8000</v>
       </c>
       <c r="K15" s="3">
         <v>8000</v>
       </c>
       <c r="L15" s="3">
+        <v>8000</v>
+      </c>
+      <c r="M15" s="3">
         <v>7900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>7800</v>
-      </c>
-      <c r="N15" s="3">
-        <v>8000</v>
       </c>
       <c r="O15" s="3">
         <v>8000</v>
       </c>
       <c r="P15" s="3">
+        <v>8000</v>
+      </c>
+      <c r="Q15" s="3">
         <v>7900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>7800</v>
-      </c>
-      <c r="R15" s="3">
-        <v>8000</v>
       </c>
       <c r="S15" s="3">
         <v>8000</v>
       </c>
       <c r="T15" s="3">
-        <v>7900</v>
+        <v>8000</v>
       </c>
       <c r="U15" s="3">
         <v>7900</v>
       </c>
       <c r="V15" s="3">
+        <v>7900</v>
+      </c>
+      <c r="W15" s="3">
         <v>8000</v>
-      </c>
-      <c r="W15" s="3">
-        <v>7600</v>
       </c>
       <c r="X15" s="3">
         <v>7600</v>
       </c>
       <c r="Y15" s="3">
+        <v>7600</v>
+      </c>
+      <c r="Z15" s="3">
         <v>7500</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>7600</v>
       </c>
       <c r="AA15" s="3">
         <v>7600</v>
@@ -1523,10 +1546,10 @@
         <v>7600</v>
       </c>
       <c r="AC15" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AD15" s="3">
         <v>7500</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>7600</v>
       </c>
       <c r="AE15" s="3">
         <v>7600</v>
@@ -1535,16 +1558,19 @@
         <v>7600</v>
       </c>
       <c r="AG15" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AH15" s="3">
         <v>7500</v>
-      </c>
-      <c r="AH15" s="3">
-        <v>7600</v>
       </c>
       <c r="AI15" s="3">
         <v>7600</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>7600</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,31 +1603,32 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>19100</v>
+        <v>19200</v>
       </c>
       <c r="E17" s="3">
+        <v>18800</v>
+      </c>
+      <c r="F17" s="3">
         <v>18700</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>8</v>
+      <c r="G17" s="3">
+        <v>19300</v>
       </c>
       <c r="H17" s="3">
+        <v>39200</v>
+      </c>
+      <c r="I17" s="3">
         <v>19400</v>
       </c>
-      <c r="I17" s="3">
-        <v>18100</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>8</v>
+      <c r="J17" s="3">
+        <v>17900</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>8</v>
@@ -1612,12 +1639,12 @@
       <c r="M17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="3">
         <v>18900</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1645,64 +1672,67 @@
       <c r="X17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Y17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z17" s="3">
         <v>17000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>19300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>19400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>18300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>17100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>17000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>17600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>23200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>17200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>17100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>18500</v>
+        <v>19800</v>
       </c>
       <c r="E18" s="3">
-        <v>19400</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>8</v>
+        <v>18800</v>
+      </c>
+      <c r="F18" s="3">
+        <v>19300</v>
+      </c>
+      <c r="G18" s="3">
+        <v>17700</v>
       </c>
       <c r="H18" s="3">
+        <v>9400</v>
+      </c>
+      <c r="I18" s="3">
         <v>18300</v>
       </c>
-      <c r="I18" s="3">
-        <v>19200</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>8</v>
+      <c r="J18" s="3">
+        <v>19300</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>8</v>
@@ -1713,12 +1743,12 @@
       <c r="M18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="3">
         <v>16800</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>8</v>
       </c>
@@ -1746,41 +1776,44 @@
       <c r="X18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z18" s="3">
         <v>14400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>11700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>11900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>12600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>16800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>17500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>15900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>8800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>21900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>24300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,31 +1849,32 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-7800</v>
+        <v>-1600</v>
       </c>
       <c r="E20" s="3">
-        <v>-7600</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>8</v>
+        <v>1300</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="G20" s="3">
+        <v>6500</v>
       </c>
       <c r="H20" s="3">
-        <v>-3900</v>
+        <v>-1200</v>
       </c>
       <c r="I20" s="3">
-        <v>-9600</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>8</v>
+        <v>-300</v>
+      </c>
+      <c r="J20" s="3">
+        <v>400</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>8</v>
@@ -1851,12 +1885,12 @@
       <c r="M20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
@@ -1884,165 +1918,171 @@
       <c r="X20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z20" s="3">
         <v>500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>300</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>200</v>
       </c>
       <c r="AB20" s="3">
         <v>200</v>
       </c>
       <c r="AC20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-100</v>
       </c>
-      <c r="AH20" s="3">
-        <v>0</v>
-      </c>
       <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>18700</v>
+        <v>29500</v>
       </c>
       <c r="E21" s="3">
-        <v>19700</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>8</v>
+        <v>25500</v>
+      </c>
+      <c r="F21" s="3">
+        <v>28400</v>
+      </c>
+      <c r="G21" s="3">
+        <v>19300</v>
       </c>
       <c r="H21" s="3">
+        <v>18600</v>
+      </c>
+      <c r="I21" s="3">
+        <v>26500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>26800</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="3">
+        <v>24900</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z21" s="3">
         <v>22400</v>
-      </c>
-      <c r="I21" s="3">
-        <v>17500</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N21" s="3">
-        <v>24900</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>22400</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>19700</v>
       </c>
       <c r="AA21" s="3">
         <v>19700</v>
       </c>
       <c r="AB21" s="3">
+        <v>19700</v>
+      </c>
+      <c r="AC21" s="3">
         <v>20400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>24300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>25100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>23400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>15100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>29200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>32000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>33600</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>7300</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>8700</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>9200</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>9200</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2068,8 +2108,8 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>8</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>8</v>
@@ -2086,65 +2126,68 @@
       <c r="X22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y22" s="3">
-        <v>13000</v>
+      <c r="Y22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z22" s="3">
         <v>13000</v>
       </c>
       <c r="AA22" s="3">
+        <v>13000</v>
+      </c>
+      <c r="AB22" s="3">
         <v>12700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>12500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>12000</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>11800</v>
       </c>
       <c r="AE22" s="3">
         <v>11800</v>
       </c>
       <c r="AF22" s="3">
+        <v>11800</v>
+      </c>
+      <c r="AG22" s="3">
         <v>12700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>8800</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>8900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E23" s="3">
         <v>10700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>11800</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G23" s="3">
+        <v>10500</v>
+      </c>
+      <c r="H23" s="3">
         <v>1400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>14400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>9600</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K23" s="3" t="s">
         <v>8</v>
       </c>
@@ -2154,12 +2197,12 @@
       <c r="M23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="3">
         <v>16900</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>8</v>
       </c>
@@ -2187,64 +2230,67 @@
       <c r="X23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Y23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z23" s="3">
         <v>1900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>5600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-5200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>12900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>15500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>17300</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -2321,8 +2367,11 @@
       <c r="AI24" s="3">
         <v>0</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,32 +2471,35 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E26" s="3">
         <v>10700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>11800</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>8</v>
+      <c r="G26" s="3">
+        <v>10500</v>
       </c>
       <c r="H26" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I26" s="3">
         <v>14400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>9600</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K26" s="3" t="s">
         <v>8</v>
       </c>
@@ -2457,12 +2509,12 @@
       <c r="M26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O26" s="3">
         <v>16900</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>8</v>
       </c>
@@ -2490,65 +2542,68 @@
       <c r="X26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Y26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z26" s="3">
         <v>1900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>5600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>4000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-5200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>12900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>15500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>17300</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>10700</v>
+        <v>15100</v>
       </c>
       <c r="E27" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F27" s="3">
         <v>11800</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>8</v>
+      <c r="G27" s="3">
+        <v>-1100</v>
       </c>
       <c r="H27" s="3">
-        <v>14400</v>
+        <v>1400</v>
       </c>
       <c r="I27" s="3">
+        <v>8600</v>
+      </c>
+      <c r="J27" s="3">
         <v>9600</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K27" s="3" t="s">
         <v>8</v>
       </c>
@@ -2558,12 +2613,12 @@
       <c r="M27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O27" s="3">
         <v>16900</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>8</v>
       </c>
@@ -2591,41 +2646,44 @@
       <c r="X27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Y27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-6900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>10000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>7900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,31 +3095,34 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>7800</v>
+        <v>1600</v>
       </c>
       <c r="E32" s="3">
-        <v>7600</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>8</v>
+        <v>-1300</v>
+      </c>
+      <c r="F32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-6500</v>
       </c>
       <c r="H32" s="3">
-        <v>3900</v>
+        <v>1200</v>
       </c>
       <c r="I32" s="3">
-        <v>9600</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>8</v>
+        <v>300</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-400</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>8</v>
@@ -3063,12 +3133,12 @@
       <c r="M32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
@@ -3096,65 +3166,68 @@
       <c r="X32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-300</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-200</v>
       </c>
       <c r="AB32" s="3">
         <v>-200</v>
       </c>
       <c r="AC32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>100</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
       <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E33" s="3">
         <v>10700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>11800</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>8</v>
+      <c r="G33" s="3">
+        <v>10500</v>
       </c>
       <c r="H33" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I33" s="3">
         <v>14400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>9600</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K33" s="3" t="s">
         <v>8</v>
       </c>
@@ -3164,12 +3237,12 @@
       <c r="M33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O33" s="3">
         <v>16900</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>8</v>
       </c>
@@ -3197,41 +3270,44 @@
       <c r="X33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Y33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-6900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>10000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>7900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,32 +3407,35 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E35" s="3">
         <v>10700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>11800</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>8</v>
+      <c r="G35" s="3">
+        <v>10500</v>
       </c>
       <c r="H35" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I35" s="3">
         <v>14400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>9600</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K35" s="3" t="s">
         <v>8</v>
       </c>
@@ -3366,12 +3445,12 @@
       <c r="M35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O35" s="3">
         <v>16900</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>8</v>
       </c>
@@ -3399,147 +3478,153 @@
       <c r="X35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Y35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-6900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>10000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>7900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,109 +3698,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E41" s="3">
         <v>35600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>76200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>73800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>64900</v>
-      </c>
-      <c r="H41" s="3">
-        <v>52900</v>
       </c>
       <c r="I41" s="3">
         <v>52900</v>
       </c>
       <c r="J41" s="3">
+        <v>52900</v>
+      </c>
+      <c r="K41" s="3">
         <v>48600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>97700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>100200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>106600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>47000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>91300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>86800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>84100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>25000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>76000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>63300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>70100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>16200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>17600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>112900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>112300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>109900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>59500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>57800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>61400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>67500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>70500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>74300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>50900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>57600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>59100</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3722,19 +3812,19 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>15600</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -3814,412 +3904,427 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>2300</v>
+      <c r="D43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E43" s="3">
+        <v>500</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="3">
+        <v>6800</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I43" s="3">
+        <v>8600</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K43" s="3">
+        <v>100</v>
+      </c>
+      <c r="L43" s="3">
         <v>1400</v>
       </c>
-      <c r="F43" s="3">
-        <v>700</v>
-      </c>
-      <c r="G43" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H43" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I43" s="3">
-        <v>1400</v>
-      </c>
-      <c r="J43" s="3">
-        <v>100</v>
-      </c>
-      <c r="K43" s="3">
-        <v>1400</v>
-      </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1700</v>
-      </c>
-      <c r="P43" s="3">
-        <v>1400</v>
       </c>
       <c r="Q43" s="3">
         <v>1400</v>
       </c>
       <c r="R43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S43" s="3">
         <v>400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>400</v>
-      </c>
-      <c r="AH43" s="3">
-        <v>1000</v>
       </c>
       <c r="AI43" s="3">
         <v>1000</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="E44" s="3">
         <v>800</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>8</v>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3">
+        <v>800</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="I44" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K44" s="3">
         <v>900</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N44" s="3">
+      <c r="N44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O44" s="3">
         <v>900</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R44" s="3">
+      <c r="R44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S44" s="3">
         <v>800</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V44" s="3">
+      <c r="V44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W44" s="3">
         <v>700</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Y44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z44" s="3">
         <v>700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>800</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AH44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI44" s="3">
         <v>800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>5000</v>
+        <v>11900</v>
       </c>
       <c r="E45" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F45" s="3">
         <v>22700</v>
       </c>
-      <c r="F45" s="3">
-        <v>30000</v>
-      </c>
       <c r="G45" s="3">
+        <v>200</v>
+      </c>
+      <c r="H45" s="3">
         <v>39200</v>
       </c>
-      <c r="H45" s="3">
-        <v>45800</v>
-      </c>
       <c r="I45" s="3">
+        <v>5900</v>
+      </c>
+      <c r="J45" s="3">
         <v>32400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>24700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>40800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>34500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>29200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>10700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>302000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>32400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>42900</v>
+        <v>63900</v>
       </c>
       <c r="E46" s="3">
+        <v>50400</v>
+      </c>
+      <c r="F46" s="3">
+        <v>98800</v>
+      </c>
+      <c r="G46" s="3">
+        <v>105300</v>
+      </c>
+      <c r="H46" s="3">
+        <v>104100</v>
+      </c>
+      <c r="I46" s="3">
         <v>100300</v>
       </c>
-      <c r="F46" s="3">
-        <v>105300</v>
-      </c>
-      <c r="G46" s="3">
-        <v>105500</v>
-      </c>
-      <c r="H46" s="3">
-        <v>100000</v>
-      </c>
-      <c r="I46" s="3">
-        <v>86600</v>
-      </c>
       <c r="J46" s="3">
+        <v>85300</v>
+      </c>
+      <c r="K46" s="3">
         <v>74200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>139900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>138500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>138600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>51200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>99900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>98800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>91900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>27100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>79900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>69300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>75100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>18200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>322100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>118200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>114800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>113000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>63500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>65700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>66100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>70400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>74700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>77700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>83700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>60200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>62000</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4229,32 +4334,32 @@
       <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
+        <v>4200</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3">
         <v>3100</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J47" s="3">
-        <v>3100</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -4319,109 +4424,115 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>773300</v>
+      </c>
+      <c r="E48" s="3">
         <v>781400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>789400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>797400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>805500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>809300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>817200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>825100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>833100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>838800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>845400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>853200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>861200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>869200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>877100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>884900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>892900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>900900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>908800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>916700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>924700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>932300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>939900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>947400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>955000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>962700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>970200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>977300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>984900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>992600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1000100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1007600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1015300</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4521,8 +4632,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>14200</v>
+        <v>3500</v>
       </c>
       <c r="E52" s="3">
-        <v>5200</v>
+        <v>5400</v>
       </c>
       <c r="F52" s="3">
-        <v>3200</v>
+        <v>6700</v>
       </c>
       <c r="G52" s="3">
-        <v>5900</v>
+        <v>3100</v>
       </c>
       <c r="H52" s="3">
-        <v>10500</v>
+        <v>7200</v>
       </c>
       <c r="I52" s="3">
-        <v>6900</v>
+        <v>3100</v>
       </c>
       <c r="J52" s="3">
+        <v>8300</v>
+      </c>
+      <c r="K52" s="3">
         <v>45200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1300</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1500</v>
       </c>
       <c r="M52" s="3">
         <v>1500</v>
       </c>
       <c r="N52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O52" s="3">
         <v>61100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>53800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>54300</v>
-      </c>
-      <c r="W52" s="3">
-        <v>3100</v>
       </c>
       <c r="X52" s="3">
         <v>3100</v>
       </c>
       <c r="Y52" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Z52" s="3">
         <v>3300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>4800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>8400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>10300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>12100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>38900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>40700</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>840700</v>
+      </c>
+      <c r="E54" s="3">
         <v>838400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>894800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>908900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>916800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>919900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>910800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>947700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>974400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>978900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>985500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>965500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>962700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>969600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>971200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>965800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>975500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>973100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>986800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>989200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1249900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1053700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1058000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1063400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1021900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1032200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1041200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1054300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1068100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1080500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1095900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1106700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1117900</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,183 +5230,187 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" s="3">
+      <c r="E57" s="3">
+        <v>12100</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G57" s="3">
         <v>13800</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="I57" s="3">
+        <v>9100</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K57" s="3">
         <v>8000</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N57" s="3">
+      <c r="N57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O57" s="3">
         <v>5700</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R57" s="3">
+      <c r="R57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S57" s="3">
         <v>4400</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V57" s="3">
+      <c r="V57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W57" s="3">
         <v>5500</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z57" s="3">
         <v>5000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>6300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>9100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>6800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>7100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>9700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>4100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>8</v>
+      <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>43600</v>
       </c>
       <c r="F58" s="3">
-        <v>419600</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
+        <v>420200</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>46500</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>46300</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N58" s="3">
+      <c r="N58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O58" s="3">
         <v>45900</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R58" s="3">
+      <c r="R58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S58" s="3">
         <v>45700</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V58" s="3">
+      <c r="V58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W58" s="3">
         <v>45500</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Y58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z58" s="3">
         <v>252000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>251800</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>2700</v>
       </c>
       <c r="AB58" s="3">
         <v>2700</v>
@@ -5288,375 +5422,387 @@
         <v>2700</v>
       </c>
       <c r="AE58" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="AF58" s="3">
         <v>2600</v>
       </c>
       <c r="AG58" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AH58" s="3">
         <v>3500</v>
-      </c>
-      <c r="AH58" s="3">
-        <v>31700</v>
       </c>
       <c r="AI58" s="3">
         <v>31700</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>31700</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>400</v>
+      <c r="D59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E59" s="3">
-        <v>27200</v>
+        <v>12900</v>
       </c>
       <c r="F59" s="3">
-        <v>25400</v>
+        <v>27100</v>
       </c>
       <c r="G59" s="3">
-        <v>42900</v>
+        <v>20500</v>
       </c>
       <c r="H59" s="3">
-        <v>32300</v>
+        <v>42200</v>
       </c>
       <c r="I59" s="3">
-        <v>23200</v>
+        <v>21100</v>
       </c>
       <c r="J59" s="3">
+        <v>20500</v>
+      </c>
+      <c r="K59" s="3">
         <v>16000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>28800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>26300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>29500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>18700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>22600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>20900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>12800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>24500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>18100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>24000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>13700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>21300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>19800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>14500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>15300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>14300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>11700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>12500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>15700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>15600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>12700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>12400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>18300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>400</v>
+      <c r="D60" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E60" s="3">
-        <v>27200</v>
+        <v>71500</v>
       </c>
       <c r="F60" s="3">
+        <v>27100</v>
+      </c>
+      <c r="G60" s="3">
         <v>458800</v>
       </c>
-      <c r="G60" s="3">
-        <v>42900</v>
-      </c>
       <c r="H60" s="3">
-        <v>32300</v>
+        <v>42200</v>
       </c>
       <c r="I60" s="3">
-        <v>23200</v>
+        <v>79100</v>
       </c>
       <c r="J60" s="3">
+        <v>20500</v>
+      </c>
+      <c r="K60" s="3">
         <v>70300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>28800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>26300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>29500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>64900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>18700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>22600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>20900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>62800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>24500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>18100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>24000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>64600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>21300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>19800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>271500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>272700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>23300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>23400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>21900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>22900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>25400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>25000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>20000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>53100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>55400</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>342500</v>
+        <v>331600</v>
       </c>
       <c r="E61" s="3">
+        <v>298900</v>
+      </c>
+      <c r="F61" s="3">
         <v>408000</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>431200</v>
       </c>
-      <c r="H61" s="3">
-        <v>442800</v>
-      </c>
       <c r="I61" s="3">
+        <v>396300</v>
+      </c>
+      <c r="J61" s="3">
         <v>454400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>450800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>527500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>539000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>550500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>516000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>573400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>584800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>596300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>562000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>619100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>630400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>641800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>607700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>914400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>712000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>460400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>461100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>710500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>710900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>711300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>711700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>712100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>712300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>710900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>684700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>692400</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>31300</v>
+        <v>33100</v>
       </c>
       <c r="E62" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3">
+        <v>5300</v>
+      </c>
+      <c r="K62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="L62" s="3">
+        <v>2800</v>
+      </c>
+      <c r="M62" s="3">
         <v>2900</v>
       </c>
-      <c r="F62" s="3">
-        <v>1900</v>
-      </c>
-      <c r="G62" s="3">
-        <v>2100</v>
-      </c>
-      <c r="H62" s="3">
-        <v>2600</v>
-      </c>
-      <c r="I62" s="3">
-        <v>2700</v>
-      </c>
-      <c r="J62" s="3">
-        <v>2700</v>
-      </c>
-      <c r="K62" s="3">
-        <v>2800</v>
-      </c>
-      <c r="L62" s="3">
-        <v>2900</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3000</v>
-      </c>
-      <c r="N62" s="3">
-        <v>3100</v>
       </c>
       <c r="O62" s="3">
         <v>3100</v>
       </c>
       <c r="P62" s="3">
-        <v>3200</v>
+        <v>3100</v>
       </c>
       <c r="Q62" s="3">
         <v>3200</v>
       </c>
       <c r="R62" s="3">
+        <v>3200</v>
+      </c>
+      <c r="S62" s="3">
         <v>4500</v>
-      </c>
-      <c r="S62" s="3">
-        <v>3200</v>
       </c>
       <c r="T62" s="3">
         <v>3200</v>
@@ -5677,37 +5823,40 @@
         <v>3200</v>
       </c>
       <c r="Z62" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="AA62" s="3">
         <v>3100</v>
       </c>
       <c r="AB62" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AC62" s="3">
         <v>1700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1100</v>
-      </c>
-      <c r="AG62" s="3">
-        <v>1000</v>
       </c>
       <c r="AH62" s="3">
         <v>1000</v>
       </c>
       <c r="AI62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>364700</v>
+      </c>
+      <c r="E66" s="3">
         <v>374200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>438100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>460700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>476200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>477700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>480200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>523800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>559200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>568200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>583000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>584000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>595200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>610600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>620400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>629300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>646800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>651800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>669000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>675500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>938800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>735000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>735100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>737000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>736900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>736000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>734700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>736000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>738700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>738400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>731900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>738800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>748800</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,31 +6514,34 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>126800</v>
+        <v>126700</v>
       </c>
       <c r="E70" s="3">
-        <v>126800</v>
+        <v>126700</v>
       </c>
       <c r="F70" s="3">
-        <v>126800</v>
+        <v>126700</v>
       </c>
       <c r="G70" s="3">
-        <v>126800</v>
+        <v>126700</v>
       </c>
       <c r="H70" s="3">
-        <v>126800</v>
+        <v>126700</v>
       </c>
       <c r="I70" s="3">
-        <v>126800</v>
+        <v>126700</v>
       </c>
       <c r="J70" s="3">
-        <v>126800</v>
+        <v>126700</v>
       </c>
       <c r="K70" s="3">
         <v>126800</v>
@@ -6388,7 +6556,7 @@
         <v>126800</v>
       </c>
       <c r="O70" s="3">
-        <v>126700</v>
+        <v>126800</v>
       </c>
       <c r="P70" s="3">
         <v>126700</v>
@@ -6421,10 +6589,10 @@
         <v>126700</v>
       </c>
       <c r="Z70" s="3">
+        <v>126700</v>
+      </c>
+      <c r="AA70" s="3">
         <v>127100</v>
-      </c>
-      <c r="AA70" s="3">
-        <v>73200</v>
       </c>
       <c r="AB70" s="3">
         <v>73200</v>
@@ -6433,7 +6601,7 @@
         <v>73200</v>
       </c>
       <c r="AD70" s="3">
-        <v>73300</v>
+        <v>73200</v>
       </c>
       <c r="AE70" s="3">
         <v>73300</v>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>73300</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>73300</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,31 +6722,34 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>0</v>
-      </c>
-      <c r="E72" s="3">
-        <v>0</v>
-      </c>
-      <c r="F72" s="3">
-        <v>0</v>
-      </c>
-      <c r="G72" s="3">
-        <v>0</v>
-      </c>
-      <c r="H72" s="3">
-        <v>0</v>
-      </c>
-      <c r="I72" s="3">
-        <v>0</v>
-      </c>
-      <c r="J72" s="3">
-        <v>0</v>
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K72" s="3">
         <v>0</v>
@@ -6652,8 +6826,11 @@
       <c r="AI72" s="3">
         <v>0</v>
       </c>
+      <c r="AJ72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>337400</v>
+        <v>349300</v>
       </c>
       <c r="E76" s="3">
-        <v>329900</v>
+        <v>337500</v>
       </c>
       <c r="F76" s="3">
-        <v>321400</v>
+        <v>330000</v>
       </c>
       <c r="G76" s="3">
-        <v>313900</v>
+        <v>321500</v>
       </c>
       <c r="H76" s="3">
-        <v>315400</v>
+        <v>314000</v>
       </c>
       <c r="I76" s="3">
-        <v>303800</v>
+        <v>315500</v>
       </c>
       <c r="J76" s="3">
+        <v>303900</v>
+      </c>
+      <c r="K76" s="3">
         <v>297100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>288400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>283900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>275700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>254700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>240700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>232300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>224000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>209800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>202000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>194600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>191100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>187000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>184400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>192000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>196200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>199400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>211800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>223000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>233200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>245100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>256100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>268900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>290700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>294500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>295800</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,138 +7346,144 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E81" s="3">
         <v>10700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>11800</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>8</v>
+      <c r="G81" s="3">
+        <v>10500</v>
       </c>
       <c r="H81" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I81" s="3">
         <v>14400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>9600</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K81" s="3" t="s">
         <v>8</v>
       </c>
@@ -7298,12 +7493,12 @@
       <c r="M81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O81" s="3">
         <v>16900</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>8</v>
       </c>
@@ -7331,41 +7526,44 @@
       <c r="X81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Y81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-6900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>10000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>7900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,8 +7599,9 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7413,7 +7612,7 @@
         <v>8000</v>
       </c>
       <c r="F83" s="3">
-        <v>8100</v>
+        <v>7900</v>
       </c>
       <c r="G83" s="3">
         <v>8000</v>
@@ -7425,55 +7624,55 @@
         <v>7900</v>
       </c>
       <c r="J83" s="3">
-        <v>8000</v>
+        <v>7800</v>
       </c>
       <c r="K83" s="3">
         <v>8000</v>
       </c>
       <c r="L83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="M83" s="3">
         <v>7900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7800</v>
-      </c>
-      <c r="N83" s="3">
-        <v>8000</v>
       </c>
       <c r="O83" s="3">
         <v>8000</v>
       </c>
       <c r="P83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="Q83" s="3">
         <v>7900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7800</v>
-      </c>
-      <c r="R83" s="3">
-        <v>8000</v>
       </c>
       <c r="S83" s="3">
         <v>8000</v>
       </c>
       <c r="T83" s="3">
-        <v>7900</v>
+        <v>8000</v>
       </c>
       <c r="U83" s="3">
         <v>7900</v>
       </c>
       <c r="V83" s="3">
+        <v>7900</v>
+      </c>
+      <c r="W83" s="3">
         <v>8000</v>
-      </c>
-      <c r="W83" s="3">
-        <v>7600</v>
       </c>
       <c r="X83" s="3">
         <v>7600</v>
       </c>
       <c r="Y83" s="3">
+        <v>7600</v>
+      </c>
+      <c r="Z83" s="3">
         <v>7500</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>7600</v>
       </c>
       <c r="AA83" s="3">
         <v>7600</v>
@@ -7482,10 +7681,10 @@
         <v>7600</v>
       </c>
       <c r="AC83" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AD83" s="3">
         <v>7500</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>7600</v>
       </c>
       <c r="AE83" s="3">
         <v>7600</v>
@@ -7494,16 +7693,19 @@
         <v>7600</v>
       </c>
       <c r="AG83" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AH83" s="3">
         <v>7500</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>7600</v>
       </c>
       <c r="AI83" s="3">
         <v>7600</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>7600</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E89" s="3">
         <v>22500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>20200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>21800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>8800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>13700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>13400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>10900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>8200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>24800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>21000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>19800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>15800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>22900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>14200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>27600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>8100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>18700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>13500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>13600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>7000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>9200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>9000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>13500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>8600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>11900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>15000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>14800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>11400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>18200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>23300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>27000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,52 +8365,53 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-2800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1300</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>8</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>8</v>
@@ -8198,8 +8419,8 @@
       <c r="S91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -8213,17 +8434,17 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>8</v>
+      <c r="AB91" s="3">
+        <v>0</v>
       </c>
       <c r="AC91" s="3" t="s">
         <v>8</v>
@@ -8237,17 +8458,20 @@
       <c r="AF91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG91" s="3">
-        <v>0</v>
+      <c r="AG91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH91" s="3">
         <v>0</v>
       </c>
       <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,44 +8675,47 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-2800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1300</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>8</v>
       </c>
@@ -8495,8 +8725,8 @@
       <c r="Q94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
+      <c r="R94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
@@ -8526,11 +8756,11 @@
         <v>0</v>
       </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-400</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
       <c r="AD94" s="3">
         <v>0</v>
       </c>
@@ -8547,10 +8777,13 @@
         <v>0</v>
       </c>
       <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +8819,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
+        <v>3300</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8646,19 +8880,19 @@
         <v>0</v>
       </c>
       <c r="V96" s="3">
-        <v>-2900</v>
+        <v>0</v>
       </c>
       <c r="W96" s="3">
         <v>-2900</v>
       </c>
       <c r="X96" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-5500</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-10600</v>
       </c>
       <c r="AA96" s="3">
         <v>-10600</v>
@@ -8667,7 +8901,7 @@
         <v>-10600</v>
       </c>
       <c r="AC96" s="3">
-        <v>-16700</v>
+        <v>-10600</v>
       </c>
       <c r="AD96" s="3">
         <v>-16700</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>-16700</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>-16700</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,100 +9233,103 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-63100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-9100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-8400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-8800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-40600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-29200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-12400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-14100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-15200</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-15300</v>
       </c>
       <c r="O100" s="3">
         <v>-15300</v>
       </c>
       <c r="P100" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-13800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-15200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-14800</v>
-      </c>
-      <c r="T100" s="3">
-        <v>-14900</v>
       </c>
       <c r="U100" s="3">
         <v>-14900</v>
       </c>
       <c r="V100" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="W100" s="3">
         <v>-264900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>191200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-6300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-6800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>41400</v>
-      </c>
-      <c r="AA100" s="3">
-        <v>-11800</v>
       </c>
       <c r="AB100" s="3">
         <v>-11800</v>
       </c>
       <c r="AC100" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-17900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-18100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-18600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>12000</v>
-      </c>
-      <c r="AG100" s="3">
-        <v>-24800</v>
       </c>
       <c r="AH100" s="3">
         <v>-24800</v>
@@ -9091,31 +9337,34 @@
       <c r="AI100" s="3">
         <v>-24800</v>
       </c>
+      <c r="AJ100" s="3">
+        <v>-24800</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9192,105 +9441,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-40600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>8800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>12000</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-27000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-17900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>9600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>5700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>9100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>12800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-6800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-251400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>204700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>50400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-6100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-3100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>23400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-6700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DLNG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DLNG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="92">
   <si>
     <t>DLNG</t>
   </si>
@@ -656,467 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>41700</v>
+      </c>
+      <c r="E8" s="3">
         <v>39100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>37600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>38100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>37000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>48600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>37700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>37300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>35100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>29900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>33400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>33300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>35700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>34700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>33900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>33400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>34400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>34300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>33900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>34500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>34300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>34400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>30800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>31400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>31000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>31300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>30900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>33900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>34500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>33500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>32000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>39100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>41400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>43100</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E9" s="3">
         <v>8900</v>
-      </c>
-      <c r="E9" s="3">
-        <v>8600</v>
       </c>
       <c r="F9" s="3">
         <v>8600</v>
       </c>
       <c r="G9" s="3">
+        <v>8600</v>
+      </c>
+      <c r="H9" s="3">
         <v>9000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>29100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>9300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>8500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7900</v>
-      </c>
-      <c r="M9" s="3">
-        <v>8200</v>
       </c>
       <c r="N9" s="3">
         <v>8200</v>
       </c>
       <c r="O9" s="3">
+        <v>8200</v>
+      </c>
+      <c r="P9" s="3">
         <v>8700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>7600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>7800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>7900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>7600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>7800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8300</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>7500</v>
       </c>
       <c r="Z9" s="3">
         <v>7500</v>
       </c>
       <c r="AA9" s="3">
+        <v>7500</v>
+      </c>
+      <c r="AB9" s="3">
         <v>7000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>7400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>6500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>7000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>7400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>6900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>8800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>7500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>7400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E10" s="3">
         <v>30100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>29000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>29500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>27900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>19500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>28400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>29300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>26600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>22000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>25200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>25100</v>
-      </c>
-      <c r="O10" s="3">
-        <v>27000</v>
       </c>
       <c r="P10" s="3">
         <v>27000</v>
       </c>
       <c r="Q10" s="3">
+        <v>27000</v>
+      </c>
+      <c r="R10" s="3">
         <v>25600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>25800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>26600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>26400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>26300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>26000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>26500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>26100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>23300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>23900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>24000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>23900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>24400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>26900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>27100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>26600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>23200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>31600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>34000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>35600</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1257,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,38 +1377,41 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>300</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
         <v>-2900</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-2100</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1408,8 +1427,8 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1465,8 +1484,11 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1474,73 +1496,73 @@
         <v>8100</v>
       </c>
       <c r="E15" s="3">
-        <v>8000</v>
+        <v>8100</v>
       </c>
       <c r="F15" s="3">
         <v>8000</v>
       </c>
       <c r="G15" s="3">
+        <v>8000</v>
+      </c>
+      <c r="H15" s="3">
         <v>8100</v>
-      </c>
-      <c r="H15" s="3">
-        <v>8000</v>
       </c>
       <c r="I15" s="3">
         <v>8000</v>
       </c>
       <c r="J15" s="3">
+        <v>8000</v>
+      </c>
+      <c r="K15" s="3">
         <v>7900</v>
-      </c>
-      <c r="K15" s="3">
-        <v>8000</v>
       </c>
       <c r="L15" s="3">
         <v>8000</v>
       </c>
       <c r="M15" s="3">
+        <v>8000</v>
+      </c>
+      <c r="N15" s="3">
         <v>7900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>7800</v>
-      </c>
-      <c r="O15" s="3">
-        <v>8000</v>
       </c>
       <c r="P15" s="3">
         <v>8000</v>
       </c>
       <c r="Q15" s="3">
+        <v>8000</v>
+      </c>
+      <c r="R15" s="3">
         <v>7900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>7800</v>
-      </c>
-      <c r="S15" s="3">
-        <v>8000</v>
       </c>
       <c r="T15" s="3">
         <v>8000</v>
       </c>
       <c r="U15" s="3">
-        <v>7900</v>
+        <v>8000</v>
       </c>
       <c r="V15" s="3">
         <v>7900</v>
       </c>
       <c r="W15" s="3">
+        <v>7900</v>
+      </c>
+      <c r="X15" s="3">
         <v>8000</v>
-      </c>
-      <c r="X15" s="3">
-        <v>7600</v>
       </c>
       <c r="Y15" s="3">
         <v>7600</v>
       </c>
       <c r="Z15" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AA15" s="3">
         <v>7500</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>7600</v>
       </c>
       <c r="AB15" s="3">
         <v>7600</v>
@@ -1549,10 +1571,10 @@
         <v>7600</v>
       </c>
       <c r="AD15" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AE15" s="3">
         <v>7500</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>7600</v>
       </c>
       <c r="AF15" s="3">
         <v>7600</v>
@@ -1561,16 +1583,19 @@
         <v>7600</v>
       </c>
       <c r="AH15" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AI15" s="3">
         <v>7500</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>7600</v>
       </c>
       <c r="AJ15" s="3">
         <v>7600</v>
       </c>
+      <c r="AK15" s="3">
+        <v>7600</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,35 +1629,36 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E17" s="3">
         <v>19200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>18800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>18700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>19300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>39200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>19400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>17900</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1642,12 +1668,12 @@
       <c r="N17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="3">
         <v>18900</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1675,68 +1701,71 @@
       <c r="Y17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="Z17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA17" s="3">
         <v>17000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>19300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>19400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>18300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>17100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>17000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>17600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>23200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>17200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>17100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E18" s="3">
         <v>19800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>18800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>19300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>17700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>9400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>18300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>19300</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>8</v>
       </c>
@@ -1746,12 +1775,12 @@
       <c r="N18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="3">
         <v>16800</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>8</v>
       </c>
@@ -1779,41 +1808,44 @@
       <c r="Y18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA18" s="3">
         <v>14400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>11700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>11900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>12600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>16800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>17500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>15900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>8800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>21900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>24300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,35 +1882,36 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>6500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
@@ -1888,12 +1921,12 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>8</v>
       </c>
@@ -1921,68 +1954,71 @@
       <c r="Y20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="Z20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA20" s="3">
         <v>500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>300</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>200</v>
       </c>
       <c r="AC20" s="3">
         <v>200</v>
       </c>
       <c r="AD20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
       <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-100</v>
       </c>
-      <c r="AI20" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E21" s="3">
         <v>29500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>25500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>28400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>19300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>18600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>26500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>26800</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1992,12 +2028,12 @@
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="3">
         <v>24900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2025,68 +2061,71 @@
       <c r="Y21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA21" s="3">
         <v>22400</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>19700</v>
       </c>
       <c r="AB21" s="3">
         <v>19700</v>
       </c>
       <c r="AC21" s="3">
+        <v>19700</v>
+      </c>
+      <c r="AD21" s="3">
         <v>20400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>24300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>25100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>23400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>15100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>29200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>32000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>33600</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E22" s="3">
         <v>6300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>8700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>4500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>4400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>9200</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -2111,8 +2150,8 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>8</v>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>8</v>
@@ -2129,68 +2168,71 @@
       <c r="Y22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z22" s="3">
-        <v>13000</v>
+      <c r="Z22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA22" s="3">
         <v>13000</v>
       </c>
       <c r="AB22" s="3">
+        <v>13000</v>
+      </c>
+      <c r="AC22" s="3">
         <v>12700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>12500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>12000</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>11800</v>
       </c>
       <c r="AF22" s="3">
         <v>11800</v>
       </c>
       <c r="AG22" s="3">
+        <v>11800</v>
+      </c>
+      <c r="AH22" s="3">
         <v>12700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>8800</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>8900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E23" s="3">
         <v>15100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>10700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>11800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>10500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>14400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9600</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>8</v>
       </c>
@@ -2200,12 +2242,12 @@
       <c r="N23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="3">
         <v>16900</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>8</v>
       </c>
@@ -2233,41 +2275,44 @@
       <c r="Y23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="Z23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA23" s="3">
         <v>1900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>5600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-5200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>12900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>15500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>17300</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2292,8 +2337,8 @@
       <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -2370,8 +2415,11 @@
       <c r="AJ24" s="3">
         <v>0</v>
       </c>
+      <c r="AK24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,35 +2522,38 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E26" s="3">
         <v>15100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>10700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>11800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>10500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>14400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>9600</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>8</v>
       </c>
@@ -2512,12 +2563,12 @@
       <c r="N26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P26" s="3">
         <v>16900</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>8</v>
       </c>
@@ -2545,68 +2596,71 @@
       <c r="Y26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="Z26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA26" s="3">
         <v>1900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>5600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>4000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-5200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>12900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>15500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>17300</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E27" s="3">
         <v>15100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>11800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>9600</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>8</v>
       </c>
@@ -2616,12 +2670,12 @@
       <c r="N27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P27" s="3">
         <v>16900</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>8</v>
       </c>
@@ -2649,41 +2703,44 @@
       <c r="Y27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="Z27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-6900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>10000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,35 +3164,38 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
         <v>1600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-6500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
@@ -3136,12 +3205,12 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>8</v>
       </c>
@@ -3169,68 +3238,71 @@
       <c r="Y32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="Z32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-300</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-200</v>
       </c>
       <c r="AC32" s="3">
         <v>-200</v>
       </c>
       <c r="AD32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
       <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>100</v>
       </c>
-      <c r="AI32" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E33" s="3">
         <v>15100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>10700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>11800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>10500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>14400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>9600</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>8</v>
       </c>
@@ -3240,12 +3312,12 @@
       <c r="N33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P33" s="3">
         <v>16900</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>8</v>
       </c>
@@ -3273,41 +3345,44 @@
       <c r="Y33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="Z33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-6900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>10000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,35 +3485,38 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E35" s="3">
         <v>15100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>10700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>11800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>10500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>14400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>9600</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>8</v>
       </c>
@@ -3448,12 +3526,12 @@
       <c r="N35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P35" s="3">
         <v>16900</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>8</v>
       </c>
@@ -3481,150 +3559,156 @@
       <c r="Y35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="Z35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-6900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>10000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3784,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>68200</v>
+      </c>
+      <c r="E41" s="3">
         <v>52000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>35600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>76200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>73800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>64900</v>
-      </c>
-      <c r="I41" s="3">
-        <v>52900</v>
       </c>
       <c r="J41" s="3">
         <v>52900</v>
       </c>
       <c r="K41" s="3">
+        <v>52900</v>
+      </c>
+      <c r="L41" s="3">
         <v>48600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>97700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>100200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>106600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>47000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>91300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>86800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>84100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>25000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>76000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>63300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>70100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>16200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>17600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>112900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>112300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>109900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>59500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>57800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>61400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>67500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>70500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>74300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>50900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>57600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>59100</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3812,23 +3901,23 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>5000</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>15600</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>24000</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -3907,424 +3996,439 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="3">
+      <c r="D43" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="3">
         <v>500</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H43" s="3">
         <v>6800</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" s="3">
         <v>8600</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1700</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>1400</v>
       </c>
       <c r="R43" s="3">
         <v>1400</v>
       </c>
       <c r="S43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="T43" s="3">
         <v>400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>400</v>
-      </c>
-      <c r="AI43" s="3">
-        <v>1000</v>
       </c>
       <c r="AJ43" s="3">
         <v>1000</v>
       </c>
+      <c r="AK43" s="3">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3">
         <v>800</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3">
         <v>800</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3">
         <v>1900</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L44" s="3">
         <v>900</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
+      <c r="O44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P44" s="3">
         <v>900</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="R44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S44" s="3">
+      <c r="S44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T44" s="3">
         <v>800</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W44" s="3">
+      <c r="W44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X44" s="3">
         <v>700</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="Z44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA44" s="3">
         <v>700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>800</v>
       </c>
-      <c r="AF44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AI44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ44" s="3">
         <v>800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E45" s="3">
         <v>11900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>22700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>39200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>32400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>24700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>40800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>34500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>29200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>10700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>302000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>32400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>81900</v>
+      </c>
+      <c r="E46" s="3">
         <v>63900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>50400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>98800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>105300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>104100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>100300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>85300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>74200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>139900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>138500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>138600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>51200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>99900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>98800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>91900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>27100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>79900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>69300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>75100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>18200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>322100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>118200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>114800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>113000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>63500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>65700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>66100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>70400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>74700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>77700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>83700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>60200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>62000</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4343,26 +4447,26 @@
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3">
         <v>4200</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3">
         <v>3100</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4427,112 +4531,118 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>765200</v>
+      </c>
+      <c r="E48" s="3">
         <v>773300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>781400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>789400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>797400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>805500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>809300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>817200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>825100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>833100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>838800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>845400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>853200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>861200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>869200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>877100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>884900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>892900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>900900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>908800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>916700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>924700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>932300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>939900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>947400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>955000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>962700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>970200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>977300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>984900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>992600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1000100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1007600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1015300</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4635,8 +4745,11 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4959,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3">
         <v>3500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>45200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1300</v>
-      </c>
-      <c r="M52" s="3">
-        <v>1500</v>
       </c>
       <c r="N52" s="3">
         <v>1500</v>
       </c>
       <c r="O52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P52" s="3">
         <v>61100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>53800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>54300</v>
-      </c>
-      <c r="X52" s="3">
-        <v>3100</v>
       </c>
       <c r="Y52" s="3">
         <v>3100</v>
       </c>
       <c r="Z52" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AA52" s="3">
         <v>3300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>4800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>6600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>8400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>10300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>12100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>38900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>40700</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>847200</v>
+      </c>
+      <c r="E54" s="3">
         <v>840700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>838400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>894800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>908900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>916800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>919900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>910800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>947700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>974400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>978900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>985500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>965500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>962700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>969600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>971200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>965800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>975500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>973100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>986800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>989200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1249900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1053700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1058000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1063400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1021900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1032200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1041200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1054300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1068100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1080500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1095900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1106700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1117900</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,112 +5360,116 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E57" s="3">
+      <c r="E57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="3">
         <v>12100</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H57" s="3">
         <v>13800</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J57" s="3">
         <v>9100</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L57" s="3">
         <v>8000</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P57" s="3">
         <v>5700</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S57" s="3">
+      <c r="S57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T57" s="3">
         <v>4400</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W57" s="3">
+      <c r="W57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X57" s="3">
         <v>5500</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="Z57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA57" s="3">
         <v>5000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>6300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>9100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>6800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>7100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>9700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>4100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>3100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5344,76 +5477,76 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>43600</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>420200</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>46500</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>46300</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="3">
+      <c r="O58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P58" s="3">
         <v>45900</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S58" s="3">
+      <c r="S58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T58" s="3">
         <v>45700</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W58" s="3">
+      <c r="W58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X58" s="3">
         <v>45500</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="Z58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA58" s="3">
         <v>252000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>251800</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>2700</v>
       </c>
       <c r="AC58" s="3">
         <v>2700</v>
@@ -5425,387 +5558,399 @@
         <v>2700</v>
       </c>
       <c r="AF58" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="AG58" s="3">
         <v>2600</v>
       </c>
       <c r="AH58" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AI58" s="3">
         <v>3500</v>
-      </c>
-      <c r="AI58" s="3">
-        <v>31700</v>
       </c>
       <c r="AJ58" s="3">
         <v>31700</v>
       </c>
+      <c r="AK58" s="3">
+        <v>31700</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="3">
         <v>12900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>27100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>20500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>42200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>21100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>20500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>16000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>28800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>26300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>29500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>18700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>22600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>20900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>24500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>18100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>24000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>13700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>21300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>19800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>14500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>15300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>14300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>11700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>12500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>15700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>15600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>12700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>12400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>18300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E60" s="3">
+      <c r="E60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60" s="3">
         <v>71500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>27100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>458800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>42200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>79100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>20500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>70300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>28800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>29500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>64900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>18700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>22600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>20900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>62800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>24500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>18100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>24000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>64600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>21300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>19800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>271500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>272700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>23300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>23400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>21900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>22900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>25400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>25000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>20000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>53100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>55400</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>320700</v>
+      </c>
+      <c r="E61" s="3">
         <v>331600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>298900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>408000</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>431200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>396300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>454400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>450800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>527500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>539000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>550500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>516000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>573400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>584800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>596300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>562000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>619100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>630400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>641800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>607700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>914400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>712000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>460400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>461100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>710500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>710900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>711300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>711700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>712100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>712300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>710900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>684700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>692400</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E62" s="3">
         <v>33100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3000</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3">
         <v>2800</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K62" s="3">
         <v>5300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3000</v>
-      </c>
-      <c r="O62" s="3">
-        <v>3100</v>
       </c>
       <c r="P62" s="3">
         <v>3100</v>
       </c>
       <c r="Q62" s="3">
-        <v>3200</v>
+        <v>3100</v>
       </c>
       <c r="R62" s="3">
         <v>3200</v>
       </c>
       <c r="S62" s="3">
+        <v>3200</v>
+      </c>
+      <c r="T62" s="3">
         <v>4500</v>
-      </c>
-      <c r="T62" s="3">
-        <v>3200</v>
       </c>
       <c r="U62" s="3">
         <v>3200</v>
@@ -5826,37 +5971,40 @@
         <v>3200</v>
       </c>
       <c r="AA62" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="AB62" s="3">
         <v>3100</v>
       </c>
       <c r="AC62" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AD62" s="3">
         <v>1700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1100</v>
-      </c>
-      <c r="AH62" s="3">
-        <v>1000</v>
       </c>
       <c r="AI62" s="3">
         <v>1000</v>
       </c>
       <c r="AJ62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AK62" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>362400</v>
+      </c>
+      <c r="E66" s="3">
         <v>364700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>374200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>438100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>460700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>476200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>477700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>480200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>523800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>559200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>568200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>583000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>584000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>595200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>610600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>620400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>629300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>646800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>651800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>669000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>675500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>938800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>735000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>735100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>737000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>736900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>736000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>734700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>736000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>738700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>738400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>731900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>738800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>748800</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6544,7 +6711,7 @@
         <v>126700</v>
       </c>
       <c r="K70" s="3">
-        <v>126800</v>
+        <v>126700</v>
       </c>
       <c r="L70" s="3">
         <v>126800</v>
@@ -6559,7 +6726,7 @@
         <v>126800</v>
       </c>
       <c r="P70" s="3">
-        <v>126700</v>
+        <v>126800</v>
       </c>
       <c r="Q70" s="3">
         <v>126700</v>
@@ -6592,10 +6759,10 @@
         <v>126700</v>
       </c>
       <c r="AA70" s="3">
+        <v>126700</v>
+      </c>
+      <c r="AB70" s="3">
         <v>127100</v>
-      </c>
-      <c r="AB70" s="3">
-        <v>73200</v>
       </c>
       <c r="AC70" s="3">
         <v>73200</v>
@@ -6604,7 +6771,7 @@
         <v>73200</v>
       </c>
       <c r="AE70" s="3">
-        <v>73300</v>
+        <v>73200</v>
       </c>
       <c r="AF70" s="3">
         <v>73300</v>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>73300</v>
       </c>
+      <c r="AK70" s="3">
+        <v>73300</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,8 +6895,11 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6751,8 +6924,8 @@
       <c r="J72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K72" s="3">
-        <v>0</v>
+      <c r="K72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L72" s="3">
         <v>0</v>
@@ -6829,8 +7002,11 @@
       <c r="AJ72" s="3">
         <v>0</v>
       </c>
+      <c r="AK72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>358100</v>
+      </c>
+      <c r="E76" s="3">
         <v>349300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>337500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>330000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>321500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>314000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>315500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>303900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>297100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>288400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>283900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>275700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>254700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>240700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>232300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>224000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>209800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>202000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>194600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>191100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>187000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>184400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>192000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>196200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>199400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>211800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>223000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>233200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>245100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>256100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>268900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>290700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>294500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>295800</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,144 +7537,150 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E81" s="3">
         <v>15100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>10700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>11800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>10500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>14400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>9600</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>8</v>
       </c>
@@ -7496,12 +7690,12 @@
       <c r="N81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P81" s="3">
         <v>16900</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>8</v>
       </c>
@@ -7529,41 +7723,44 @@
       <c r="Y81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="Z81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-6900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>10000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,82 +7797,83 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>8000</v>
+        <v>8100</v>
       </c>
       <c r="E83" s="3">
         <v>8000</v>
       </c>
       <c r="F83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="G83" s="3">
         <v>7900</v>
-      </c>
-      <c r="G83" s="3">
-        <v>8000</v>
       </c>
       <c r="H83" s="3">
         <v>8000</v>
       </c>
       <c r="I83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="J83" s="3">
         <v>7900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7800</v>
-      </c>
-      <c r="K83" s="3">
-        <v>8000</v>
       </c>
       <c r="L83" s="3">
         <v>8000</v>
       </c>
       <c r="M83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="N83" s="3">
         <v>7900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7800</v>
-      </c>
-      <c r="O83" s="3">
-        <v>8000</v>
       </c>
       <c r="P83" s="3">
         <v>8000</v>
       </c>
       <c r="Q83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="R83" s="3">
         <v>7900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7800</v>
-      </c>
-      <c r="S83" s="3">
-        <v>8000</v>
       </c>
       <c r="T83" s="3">
         <v>8000</v>
       </c>
       <c r="U83" s="3">
-        <v>7900</v>
+        <v>8000</v>
       </c>
       <c r="V83" s="3">
         <v>7900</v>
       </c>
       <c r="W83" s="3">
+        <v>7900</v>
+      </c>
+      <c r="X83" s="3">
         <v>8000</v>
-      </c>
-      <c r="X83" s="3">
-        <v>7600</v>
       </c>
       <c r="Y83" s="3">
         <v>7600</v>
       </c>
       <c r="Z83" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AA83" s="3">
         <v>7500</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>7600</v>
       </c>
       <c r="AB83" s="3">
         <v>7600</v>
@@ -7684,10 +7882,10 @@
         <v>7600</v>
       </c>
       <c r="AD83" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AE83" s="3">
         <v>7500</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>7600</v>
       </c>
       <c r="AF83" s="3">
         <v>7600</v>
@@ -7696,16 +7894,19 @@
         <v>7600</v>
       </c>
       <c r="AH83" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AI83" s="3">
         <v>7500</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>7600</v>
       </c>
       <c r="AJ83" s="3">
         <v>7600</v>
       </c>
+      <c r="AK83" s="3">
+        <v>7600</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E89" s="3">
         <v>25600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>22500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>11600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>20200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>21800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>8800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>13700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>13400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>8200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>24800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>21000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>19800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>15800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>22900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>14200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>27600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>8100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>18700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>13500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>13600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>7000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>9200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>9000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>13500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>8600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>11900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>15000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>14800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>11400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>18200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>23300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>27000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,55 +8585,56 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-2800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1300</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>8</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>8</v>
@@ -8422,8 +8642,8 @@
       <c r="T91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -8437,17 +8657,17 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>0</v>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>8</v>
+      <c r="AC91" s="3">
+        <v>0</v>
       </c>
       <c r="AD91" s="3" t="s">
         <v>8</v>
@@ -8461,17 +8681,20 @@
       <c r="AG91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH91" s="3">
-        <v>0</v>
+      <c r="AH91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI91" s="3">
         <v>0</v>
       </c>
       <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,47 +8904,50 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-2800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1300</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>8</v>
       </c>
@@ -8728,8 +8957,8 @@
       <c r="R94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
@@ -8759,11 +8988,11 @@
         <v>0</v>
       </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-400</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
-      </c>
       <c r="AE94" s="3">
         <v>0</v>
       </c>
@@ -8780,10 +9009,13 @@
         <v>0</v>
       </c>
       <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK94" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,35 +9052,36 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>8</v>
+      <c r="D96" s="3">
+        <v>5000</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F96" s="3">
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3">
         <v>3300</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H96" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3">
         <v>2900</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -8883,19 +9116,19 @@
         <v>0</v>
       </c>
       <c r="W96" s="3">
-        <v>-2900</v>
+        <v>0</v>
       </c>
       <c r="X96" s="3">
         <v>-2900</v>
       </c>
       <c r="Y96" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-5500</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-10600</v>
       </c>
       <c r="AB96" s="3">
         <v>-10600</v>
@@ -8904,7 +9137,7 @@
         <v>-10600</v>
       </c>
       <c r="AD96" s="3">
-        <v>-16700</v>
+        <v>-10600</v>
       </c>
       <c r="AE96" s="3">
         <v>-16700</v>
@@ -8924,8 +9157,11 @@
       <c r="AJ96" s="3">
         <v>-16700</v>
       </c>
+      <c r="AK96" s="3">
+        <v>-16700</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,103 +9478,106 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-9100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-63100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-9100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-8500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-8400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-8800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-40600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-29200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-12400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-14100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-15200</v>
-      </c>
-      <c r="O100" s="3">
-        <v>-15300</v>
       </c>
       <c r="P100" s="3">
         <v>-15300</v>
       </c>
       <c r="Q100" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="R100" s="3">
         <v>-13100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-13800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-15200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-14800</v>
-      </c>
-      <c r="U100" s="3">
-        <v>-14900</v>
       </c>
       <c r="V100" s="3">
         <v>-14900</v>
       </c>
       <c r="W100" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="X100" s="3">
         <v>-264900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>191200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-6300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-6800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>41400</v>
-      </c>
-      <c r="AB100" s="3">
-        <v>-11800</v>
       </c>
       <c r="AC100" s="3">
         <v>-11800</v>
       </c>
       <c r="AD100" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-17900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-18100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-18600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>12000</v>
-      </c>
-      <c r="AH100" s="3">
-        <v>-24800</v>
       </c>
       <c r="AI100" s="3">
         <v>-24800</v>
@@ -9340,8 +9585,11 @@
       <c r="AJ100" s="3">
         <v>-24800</v>
       </c>
+      <c r="AK100" s="3">
+        <v>-24800</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9366,8 +9614,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9444,108 +9692,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E102" s="3">
         <v>16500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-40600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>8800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>12000</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-27000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-17900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>9600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>5700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>9100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>12800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-6800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-251400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>204700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>50400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>23400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-6700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DLNG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DLNG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="92">
   <si>
     <t>DLNG</t>
   </si>
@@ -1385,8 +1385,8 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1398,7 +1398,7 @@
         <v>8</v>
       </c>
       <c r="H14" s="3">
-        <v>-2900</v>
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
@@ -1889,7 +1889,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-100</v>
+        <v>1800</v>
       </c>
       <c r="E20" s="3">
         <v>-1600</v>
@@ -1901,7 +1901,7 @@
         <v>-1100</v>
       </c>
       <c r="H20" s="3">
-        <v>6500</v>
+        <v>3600</v>
       </c>
       <c r="I20" s="3">
         <v>-1200</v>
@@ -1996,7 +1996,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>27600</v>
+        <v>25700</v>
       </c>
       <c r="E21" s="3">
         <v>29500</v>
@@ -2008,7 +2008,7 @@
         <v>28400</v>
       </c>
       <c r="H21" s="3">
-        <v>19300</v>
+        <v>22100</v>
       </c>
       <c r="I21" s="3">
         <v>18600</v>
@@ -2103,7 +2103,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>5500</v>
+        <v>5100</v>
       </c>
       <c r="E22" s="3">
         <v>6300</v>
@@ -2638,7 +2638,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>14100</v>
+        <v>1100</v>
       </c>
       <c r="E27" s="3">
         <v>15100</v>
@@ -3173,7 +3173,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>100</v>
+        <v>-1800</v>
       </c>
       <c r="E32" s="3">
         <v>1600</v>
@@ -3185,7 +3185,7 @@
         <v>1100</v>
       </c>
       <c r="H32" s="3">
-        <v>-6500</v>
+        <v>-3600</v>
       </c>
       <c r="I32" s="3">
         <v>1200</v>
@@ -4005,7 +4005,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2500</v>
+        <v>3900</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>8</v>
@@ -4111,8 +4111,8 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>8</v>
+      <c r="D44" s="3">
+        <v>900</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>8</v>
@@ -4219,7 +4219,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>11200</v>
+        <v>1400</v>
       </c>
       <c r="E45" s="3">
         <v>11900</v>
@@ -4326,7 +4326,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>81900</v>
+        <v>78200</v>
       </c>
       <c r="E46" s="3">
         <v>63900</v>
@@ -4967,8 +4967,8 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>8</v>
+      <c r="D52" s="3">
+        <v>3100</v>
       </c>
       <c r="E52" s="3">
         <v>3500</v>
@@ -5366,8 +5366,8 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>8</v>
+      <c r="D57" s="3">
+        <v>13200</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>8</v>
@@ -5474,7 +5474,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>43600</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -5580,8 +5580,8 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>8</v>
+      <c r="D59" s="3">
+        <v>20800</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>8</v>
@@ -5687,8 +5687,8 @@
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>8</v>
+      <c r="D60" s="3">
+        <v>83900</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>8</v>
@@ -5795,7 +5795,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>320700</v>
+        <v>277100</v>
       </c>
       <c r="E61" s="3">
         <v>331600</v>
@@ -5901,8 +5901,8 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>41600</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E62" s="3">
         <v>33100</v>
@@ -8591,8 +8591,8 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>8</v>
+      <c r="D91" s="3">
+        <v>0</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>8</v>
@@ -8912,8 +8912,8 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>8</v>
+      <c r="D94" s="3">
+        <v>0</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>8</v>
@@ -9058,8 +9058,8 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>5000</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>8</v>

--- a/AAII_Financials/Quarterly/DLNG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DLNG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="92">
   <si>
     <t>DLNG</t>
   </si>
@@ -656,479 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3">
         <v>41700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3">
+        <v>37600</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3">
+        <v>37000</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="3">
+        <v>37700</v>
+      </c>
+      <c r="L8" s="3">
+        <v>37300</v>
+      </c>
+      <c r="M8" s="3">
+        <v>35100</v>
+      </c>
+      <c r="N8" s="3">
+        <v>29900</v>
+      </c>
+      <c r="O8" s="3">
+        <v>33400</v>
+      </c>
+      <c r="P8" s="3">
+        <v>33300</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>35700</v>
+      </c>
+      <c r="R8" s="3">
+        <v>34700</v>
+      </c>
+      <c r="S8" s="3">
+        <v>33900</v>
+      </c>
+      <c r="T8" s="3">
+        <v>33400</v>
+      </c>
+      <c r="U8" s="3">
+        <v>34400</v>
+      </c>
+      <c r="V8" s="3">
+        <v>34300</v>
+      </c>
+      <c r="W8" s="3">
+        <v>33900</v>
+      </c>
+      <c r="X8" s="3">
+        <v>34500</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>34300</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>34400</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>30800</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>31400</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>31000</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>31300</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>30900</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>33900</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>34500</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>33500</v>
+      </c>
+      <c r="AI8" s="3">
+        <v>32000</v>
+      </c>
+      <c r="AJ8" s="3">
         <v>39100</v>
       </c>
-      <c r="F8" s="3">
-        <v>37600</v>
-      </c>
-      <c r="G8" s="3">
-        <v>38100</v>
-      </c>
-      <c r="H8" s="3">
-        <v>37000</v>
-      </c>
-      <c r="I8" s="3">
-        <v>48600</v>
-      </c>
-      <c r="J8" s="3">
-        <v>37700</v>
-      </c>
-      <c r="K8" s="3">
-        <v>37300</v>
-      </c>
-      <c r="L8" s="3">
-        <v>35100</v>
-      </c>
-      <c r="M8" s="3">
-        <v>29900</v>
-      </c>
-      <c r="N8" s="3">
-        <v>33400</v>
-      </c>
-      <c r="O8" s="3">
-        <v>33300</v>
-      </c>
-      <c r="P8" s="3">
-        <v>35700</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>34700</v>
-      </c>
-      <c r="R8" s="3">
-        <v>33900</v>
-      </c>
-      <c r="S8" s="3">
-        <v>33400</v>
-      </c>
-      <c r="T8" s="3">
-        <v>34400</v>
-      </c>
-      <c r="U8" s="3">
-        <v>34300</v>
-      </c>
-      <c r="V8" s="3">
-        <v>33900</v>
-      </c>
-      <c r="W8" s="3">
-        <v>34500</v>
-      </c>
-      <c r="X8" s="3">
-        <v>34300</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>34400</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>30800</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>31400</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>31000</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>31300</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>30900</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>33900</v>
-      </c>
-      <c r="AF8" s="3">
-        <v>34500</v>
-      </c>
-      <c r="AG8" s="3">
-        <v>33500</v>
-      </c>
-      <c r="AH8" s="3">
-        <v>32000</v>
-      </c>
-      <c r="AI8" s="3">
-        <v>39100</v>
-      </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>41400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>43100</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3">
         <v>12000</v>
       </c>
-      <c r="E9" s="3">
-        <v>8900</v>
-      </c>
-      <c r="F9" s="3">
-        <v>8600</v>
+      <c r="F9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G9" s="3">
         <v>8600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3">
         <v>9000</v>
       </c>
-      <c r="I9" s="3">
-        <v>29100</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="J9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
         <v>9300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>8000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7900</v>
-      </c>
-      <c r="N9" s="3">
-        <v>8200</v>
       </c>
       <c r="O9" s="3">
         <v>8200</v>
       </c>
       <c r="P9" s="3">
+        <v>8200</v>
+      </c>
+      <c r="Q9" s="3">
         <v>8700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>7700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>7600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>7800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>7900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>7600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>7800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8300</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>7500</v>
       </c>
       <c r="AA9" s="3">
         <v>7500</v>
       </c>
       <c r="AB9" s="3">
+        <v>7500</v>
+      </c>
+      <c r="AC9" s="3">
         <v>7000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>7400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>6500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>7000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>7400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>6900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>8800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>7500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>7400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3">
         <v>29600</v>
       </c>
-      <c r="E10" s="3">
-        <v>30100</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="F10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3">
         <v>29000</v>
       </c>
-      <c r="G10" s="3">
-        <v>29500</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3">
         <v>27900</v>
       </c>
-      <c r="I10" s="3">
-        <v>19500</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="J10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="3">
         <v>28400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>29300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>26600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>22000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>25200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>25100</v>
-      </c>
-      <c r="P10" s="3">
-        <v>27000</v>
       </c>
       <c r="Q10" s="3">
         <v>27000</v>
       </c>
       <c r="R10" s="3">
+        <v>27000</v>
+      </c>
+      <c r="S10" s="3">
         <v>25600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>25800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>26600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>26400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>26300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>26000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>26500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>26100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>23300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>23900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>24000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>23900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>24400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>26900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>27100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>26600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>23200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>31600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>34000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>35600</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1273,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,41 +1397,44 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-2100</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1430,8 +1450,8 @@
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1487,85 +1507,88 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>8100</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
         <v>8100</v>
       </c>
       <c r="F15" s="3">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
         <v>8000</v>
       </c>
       <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
         <v>8100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
         <v>8000</v>
       </c>
-      <c r="J15" s="3">
-        <v>8000</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>7900</v>
-      </c>
-      <c r="L15" s="3">
-        <v>8000</v>
       </c>
       <c r="M15" s="3">
         <v>8000</v>
       </c>
       <c r="N15" s="3">
+        <v>8000</v>
+      </c>
+      <c r="O15" s="3">
         <v>7900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>7800</v>
-      </c>
-      <c r="P15" s="3">
-        <v>8000</v>
       </c>
       <c r="Q15" s="3">
         <v>8000</v>
       </c>
       <c r="R15" s="3">
+        <v>8000</v>
+      </c>
+      <c r="S15" s="3">
         <v>7900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>7800</v>
-      </c>
-      <c r="T15" s="3">
-        <v>8000</v>
       </c>
       <c r="U15" s="3">
         <v>8000</v>
       </c>
       <c r="V15" s="3">
-        <v>7900</v>
+        <v>8000</v>
       </c>
       <c r="W15" s="3">
         <v>7900</v>
       </c>
       <c r="X15" s="3">
+        <v>7900</v>
+      </c>
+      <c r="Y15" s="3">
         <v>8000</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>7600</v>
       </c>
       <c r="Z15" s="3">
         <v>7600</v>
       </c>
       <c r="AA15" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AB15" s="3">
         <v>7500</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>7600</v>
       </c>
       <c r="AC15" s="3">
         <v>7600</v>
@@ -1574,10 +1597,10 @@
         <v>7600</v>
       </c>
       <c r="AE15" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AF15" s="3">
         <v>7500</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>7600</v>
       </c>
       <c r="AG15" s="3">
         <v>7600</v>
@@ -1586,16 +1609,19 @@
         <v>7600</v>
       </c>
       <c r="AI15" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>7500</v>
-      </c>
-      <c r="AJ15" s="3">
-        <v>7600</v>
       </c>
       <c r="AK15" s="3">
         <v>7600</v>
       </c>
+      <c r="AL15" s="3">
+        <v>7600</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,38 +1656,39 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3">
         <v>22200</v>
       </c>
-      <c r="E17" s="3">
-        <v>19200</v>
-      </c>
-      <c r="F17" s="3">
+      <c r="F17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3">
         <v>18800</v>
       </c>
-      <c r="G17" s="3">
-        <v>18700</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="H17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="3">
         <v>19300</v>
       </c>
-      <c r="I17" s="3">
-        <v>39200</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="J17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="3">
         <v>19400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17900</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1671,12 +1698,12 @@
       <c r="O17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P17" s="3">
+      <c r="P17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="3">
         <v>18900</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1704,71 +1731,74 @@
       <c r="Z17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AA17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB17" s="3">
         <v>17000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>19300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>19400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>18300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>17100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>17000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>17600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>23200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>17200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>17100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3">
         <v>19400</v>
       </c>
-      <c r="E18" s="3">
-        <v>19800</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="F18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3">
         <v>18800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="3">
+        <v>17700</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="3">
+        <v>18300</v>
+      </c>
+      <c r="L18" s="3">
         <v>19300</v>
       </c>
-      <c r="H18" s="3">
-        <v>17700</v>
-      </c>
-      <c r="I18" s="3">
-        <v>9400</v>
-      </c>
-      <c r="J18" s="3">
-        <v>18300</v>
-      </c>
-      <c r="K18" s="3">
-        <v>19300</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>8</v>
       </c>
@@ -1778,12 +1808,12 @@
       <c r="O18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="3">
         <v>16800</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>8</v>
       </c>
@@ -1811,41 +1841,44 @@
       <c r="Z18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB18" s="3">
         <v>14400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>11700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>11900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>12600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>16800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>17500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>15900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>8800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>21900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>24300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,38 +1916,39 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3">
         <v>1800</v>
       </c>
-      <c r="E20" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3">
         <v>1300</v>
       </c>
-      <c r="G20" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3">
         <v>3600</v>
       </c>
-      <c r="I20" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>8</v>
       </c>
@@ -1924,12 +1958,12 @@
       <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>8</v>
       </c>
@@ -1957,71 +1991,74 @@
       <c r="Z20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB20" s="3">
         <v>500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>300</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>200</v>
       </c>
       <c r="AD20" s="3">
         <v>200</v>
       </c>
       <c r="AE20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AF20" s="3">
         <v>0</v>
       </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ20" s="3">
-        <v>0</v>
-      </c>
       <c r="AK20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
         <v>25700</v>
       </c>
-      <c r="E21" s="3">
-        <v>29500</v>
-      </c>
       <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
         <v>25500</v>
       </c>
-      <c r="G21" s="3">
-        <v>28400</v>
-      </c>
       <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>22100</v>
       </c>
-      <c r="I21" s="3">
-        <v>18600</v>
-      </c>
       <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
         <v>26500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>26800</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2031,12 +2068,12 @@
       <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="3">
         <v>24900</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2064,71 +2101,74 @@
       <c r="Z21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB21" s="3">
         <v>22400</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>19700</v>
       </c>
       <c r="AC21" s="3">
         <v>19700</v>
       </c>
       <c r="AD21" s="3">
+        <v>19700</v>
+      </c>
+      <c r="AE21" s="3">
         <v>20400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>24300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>25100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>23400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>15100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>29200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>32000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>33600</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3">
         <v>5100</v>
       </c>
-      <c r="E22" s="3">
-        <v>6300</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3">
         <v>7300</v>
       </c>
-      <c r="G22" s="3">
-        <v>8700</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3">
         <v>4500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3">
+        <v>4400</v>
+      </c>
+      <c r="L22" s="3">
         <v>9200</v>
       </c>
-      <c r="J22" s="3">
-        <v>4400</v>
-      </c>
-      <c r="K22" s="3">
-        <v>9200</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -2153,8 +2193,8 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>8</v>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>8</v>
@@ -2171,71 +2211,74 @@
       <c r="Z22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA22" s="3">
-        <v>13000</v>
+      <c r="AA22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB22" s="3">
         <v>13000</v>
       </c>
       <c r="AC22" s="3">
+        <v>13000</v>
+      </c>
+      <c r="AD22" s="3">
         <v>12700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>12500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>12000</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>11800</v>
       </c>
       <c r="AG22" s="3">
         <v>11800</v>
       </c>
       <c r="AH22" s="3">
+        <v>11800</v>
+      </c>
+      <c r="AI22" s="3">
         <v>12700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>8800</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>8900</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3">
         <v>14100</v>
       </c>
-      <c r="E23" s="3">
-        <v>15100</v>
-      </c>
-      <c r="F23" s="3">
+      <c r="F23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3">
         <v>10700</v>
       </c>
-      <c r="G23" s="3">
-        <v>11800</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="H23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="3">
         <v>10500</v>
       </c>
-      <c r="I23" s="3">
-        <v>1400</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="J23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="3">
         <v>14400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>9600</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>8</v>
       </c>
@@ -2245,12 +2288,12 @@
       <c r="O23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P23" s="3">
+      <c r="P23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="3">
         <v>16900</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>8</v>
       </c>
@@ -2278,41 +2321,44 @@
       <c r="Z23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AA23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB23" s="3">
         <v>1900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>5600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>4000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-5200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>12900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>15500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>17300</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2340,8 +2386,8 @@
       <c r="K24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -2418,8 +2464,11 @@
       <c r="AK24" s="3">
         <v>0</v>
       </c>
+      <c r="AL24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,38 +2574,41 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3">
         <v>14100</v>
       </c>
-      <c r="E26" s="3">
-        <v>15100</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="F26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3">
         <v>10700</v>
       </c>
-      <c r="G26" s="3">
-        <v>11800</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="H26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="3">
         <v>10500</v>
       </c>
-      <c r="I26" s="3">
-        <v>1400</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="J26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="3">
         <v>14400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>9600</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>8</v>
       </c>
@@ -2566,12 +2618,12 @@
       <c r="O26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P26" s="3">
+      <c r="P26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q26" s="3">
         <v>16900</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>8</v>
       </c>
@@ -2599,71 +2651,74 @@
       <c r="Z26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AA26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB26" s="3">
         <v>1900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>4800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>5600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>4000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-5200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>12900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>15500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>17300</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3">
         <v>1100</v>
       </c>
-      <c r="E27" s="3">
-        <v>15100</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="F27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3">
         <v>4200</v>
       </c>
-      <c r="G27" s="3">
-        <v>11800</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="H27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="3">
         <v>-1100</v>
       </c>
-      <c r="I27" s="3">
-        <v>1400</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="J27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="3">
         <v>8600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>9600</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>8</v>
       </c>
@@ -2673,12 +2728,12 @@
       <c r="O27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P27" s="3">
+      <c r="P27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q27" s="3">
         <v>16900</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>8</v>
       </c>
@@ -2706,41 +2761,44 @@
       <c r="Z27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AA27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-6900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>10000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>7900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,38 +3234,41 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1800</v>
       </c>
-      <c r="E32" s="3">
-        <v>1600</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3">
         <v>-1300</v>
       </c>
-      <c r="G32" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3">
         <v>-3600</v>
       </c>
-      <c r="I32" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>8</v>
       </c>
@@ -3208,12 +3278,12 @@
       <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>8</v>
       </c>
@@ -3241,71 +3311,74 @@
       <c r="Z32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-300</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-200</v>
       </c>
       <c r="AD32" s="3">
         <v>-200</v>
       </c>
       <c r="AE32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="AF32" s="3">
         <v>0</v>
       </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>100</v>
       </c>
-      <c r="AJ32" s="3">
-        <v>0</v>
-      </c>
       <c r="AK32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3">
         <v>14100</v>
       </c>
-      <c r="E33" s="3">
-        <v>15100</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="F33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="3">
         <v>10700</v>
       </c>
-      <c r="G33" s="3">
-        <v>11800</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="H33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" s="3">
         <v>10500</v>
       </c>
-      <c r="I33" s="3">
-        <v>1400</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="J33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" s="3">
         <v>14400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>9600</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>8</v>
       </c>
@@ -3315,12 +3388,12 @@
       <c r="O33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P33" s="3">
+      <c r="P33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q33" s="3">
         <v>16900</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>8</v>
       </c>
@@ -3348,41 +3421,44 @@
       <c r="Z33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AA33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-6900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>10000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>7900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,38 +3564,41 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3">
         <v>14100</v>
       </c>
-      <c r="E35" s="3">
-        <v>15100</v>
-      </c>
-      <c r="F35" s="3">
+      <c r="F35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="3">
         <v>10700</v>
       </c>
-      <c r="G35" s="3">
-        <v>11800</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="H35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" s="3">
         <v>10500</v>
       </c>
-      <c r="I35" s="3">
-        <v>1400</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="J35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="3">
         <v>14400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>9600</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>8</v>
       </c>
@@ -3529,12 +3608,12 @@
       <c r="O35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P35" s="3">
+      <c r="P35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q35" s="3">
         <v>16900</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>8</v>
       </c>
@@ -3562,153 +3641,159 @@
       <c r="Z35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AA35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-6900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>10000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>7900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,115 +3871,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="3">
         <v>68200</v>
       </c>
-      <c r="E41" s="3">
-        <v>52000</v>
-      </c>
-      <c r="F41" s="3">
+      <c r="F41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G41" s="3">
         <v>35600</v>
       </c>
-      <c r="G41" s="3">
-        <v>76200</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I41" s="3">
         <v>73800</v>
       </c>
-      <c r="I41" s="3">
-        <v>64900</v>
-      </c>
-      <c r="J41" s="3">
-        <v>52900</v>
+      <c r="J41" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K41" s="3">
         <v>52900</v>
       </c>
       <c r="L41" s="3">
+        <v>52900</v>
+      </c>
+      <c r="M41" s="3">
         <v>48600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>97700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>100200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>106600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>47000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>91300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>86800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>84100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>25000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>76000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>63300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>70100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>16200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>17600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>112900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>112300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>109900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>59500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>57800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>61400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>67500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>70500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>74300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>50900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>57600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>59100</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3904,23 +3994,23 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>5000</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>15600</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>24000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3999,436 +4089,451 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3">
         <v>3900</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" s="3">
+      <c r="F43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="3">
         <v>500</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I43" s="3">
         <v>6800</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K43" s="3">
         <v>8600</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M43" s="3">
         <v>100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1700</v>
-      </c>
-      <c r="R43" s="3">
-        <v>1400</v>
       </c>
       <c r="S43" s="3">
         <v>1400</v>
       </c>
       <c r="T43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="U43" s="3">
         <v>400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>400</v>
-      </c>
-      <c r="AJ43" s="3">
-        <v>1000</v>
       </c>
       <c r="AK43" s="3">
         <v>1000</v>
       </c>
+      <c r="AL43" s="3">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3">
         <v>900</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3">
         <v>800</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3">
         <v>800</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="J44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K44" s="3">
         <v>1900</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M44" s="3">
         <v>900</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P44" s="3">
+      <c r="P44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q44" s="3">
         <v>900</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T44" s="3">
+      <c r="T44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U44" s="3">
         <v>800</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X44" s="3">
+      <c r="X44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y44" s="3">
         <v>700</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AA44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB44" s="3">
         <v>700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>800</v>
       </c>
-      <c r="AG44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AJ44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK44" s="3">
         <v>800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>1400</v>
       </c>
-      <c r="E45" s="3">
-        <v>11900</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3">
         <v>5400</v>
       </c>
-      <c r="G45" s="3">
-        <v>22700</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3">
         <v>200</v>
       </c>
-      <c r="I45" s="3">
-        <v>39200</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>5900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>32400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>24700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>40800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>34500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>29200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>302000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>32400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="3">
         <v>78200</v>
       </c>
-      <c r="E46" s="3">
-        <v>63900</v>
-      </c>
-      <c r="F46" s="3">
+      <c r="F46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G46" s="3">
         <v>50400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I46" s="3">
+        <v>105300</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K46" s="3">
+        <v>100300</v>
+      </c>
+      <c r="L46" s="3">
+        <v>85300</v>
+      </c>
+      <c r="M46" s="3">
+        <v>74200</v>
+      </c>
+      <c r="N46" s="3">
+        <v>139900</v>
+      </c>
+      <c r="O46" s="3">
+        <v>138500</v>
+      </c>
+      <c r="P46" s="3">
+        <v>138600</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>51200</v>
+      </c>
+      <c r="R46" s="3">
+        <v>99900</v>
+      </c>
+      <c r="S46" s="3">
         <v>98800</v>
       </c>
-      <c r="H46" s="3">
-        <v>105300</v>
-      </c>
-      <c r="I46" s="3">
-        <v>104100</v>
-      </c>
-      <c r="J46" s="3">
-        <v>100300</v>
-      </c>
-      <c r="K46" s="3">
-        <v>85300</v>
-      </c>
-      <c r="L46" s="3">
-        <v>74200</v>
-      </c>
-      <c r="M46" s="3">
-        <v>139900</v>
-      </c>
-      <c r="N46" s="3">
-        <v>138500</v>
-      </c>
-      <c r="O46" s="3">
-        <v>138600</v>
-      </c>
-      <c r="P46" s="3">
-        <v>51200</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>99900</v>
-      </c>
-      <c r="R46" s="3">
-        <v>98800</v>
-      </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>91900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>27100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>79900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>69300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>75100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>18200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>322100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>118200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>114800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>113000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>63500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>65700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>66100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>70400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>74700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>77700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>83700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>60200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>62000</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4450,26 +4555,26 @@
       <c r="I47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3">
         <v>4200</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3">
         <v>3100</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4534,138 +4639,144 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3">
         <v>765200</v>
       </c>
-      <c r="E48" s="3">
-        <v>773300</v>
-      </c>
-      <c r="F48" s="3">
+      <c r="F48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G48" s="3">
         <v>781400</v>
       </c>
-      <c r="G48" s="3">
-        <v>789400</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I48" s="3">
         <v>797400</v>
       </c>
-      <c r="I48" s="3">
-        <v>805500</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K48" s="3">
         <v>809300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>817200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>825100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>833100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>838800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>845400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>853200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>861200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>869200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>877100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>884900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>892900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>900900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>908800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>916700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>924700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>932300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>939900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>947400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>955000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>962700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>970200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>977300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>984900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>992600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1000100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1007600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1015300</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>0</v>
+      <c r="D49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
+      <c r="F49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G49" s="3">
         <v>0</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
+      <c r="H49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
+      <c r="J49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -4748,8 +4859,11 @@
       <c r="AK49" s="3">
         <v>0</v>
       </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,115 +5079,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3">
         <v>3100</v>
       </c>
-      <c r="E52" s="3">
-        <v>3500</v>
-      </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3">
         <v>5400</v>
       </c>
-      <c r="G52" s="3">
-        <v>6700</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3">
         <v>3100</v>
       </c>
-      <c r="I52" s="3">
-        <v>7200</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K52" s="3">
         <v>3100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>45200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1300</v>
-      </c>
-      <c r="N52" s="3">
-        <v>1500</v>
       </c>
       <c r="O52" s="3">
         <v>1500</v>
       </c>
       <c r="P52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q52" s="3">
         <v>61100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>53800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>54300</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>3100</v>
       </c>
       <c r="Z52" s="3">
         <v>3100</v>
       </c>
       <c r="AA52" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AB52" s="3">
         <v>3300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>4800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>6600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>8400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>10300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>12100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>38900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>40700</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="3">
         <v>847200</v>
       </c>
-      <c r="E54" s="3">
-        <v>840700</v>
-      </c>
-      <c r="F54" s="3">
+      <c r="F54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G54" s="3">
         <v>838400</v>
       </c>
-      <c r="G54" s="3">
-        <v>894800</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I54" s="3">
         <v>908900</v>
       </c>
-      <c r="I54" s="3">
-        <v>916800</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K54" s="3">
         <v>919900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>910800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>947700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>974400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>978900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>985500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>965500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>962700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>969600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>971200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>965800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>975500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>973100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>986800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>989200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1249900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1053700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1058000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1063400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1021900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1032200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1041200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1054300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1068100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1080500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1095900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1106700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1117900</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,195 +5491,199 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3">
         <v>13200</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" s="3">
+      <c r="F57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G57" s="3">
         <v>12100</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3">
         <v>13800</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K57" s="3">
         <v>9100</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M57" s="3">
         <v>8000</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q57" s="3">
         <v>5700</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T57" s="3">
+      <c r="T57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U57" s="3">
         <v>4400</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X57" s="3">
+      <c r="X57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y57" s="3">
         <v>5500</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB57" s="3">
         <v>5000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>6300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>6800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>7100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>9700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>4100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3100</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="3">
         <v>43600</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
+      <c r="F58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G58" s="3">
         <v>43600</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I58" s="3">
         <v>420200</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="J58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K58" s="3">
         <v>46500</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>46300</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P58" s="3">
+      <c r="P58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q58" s="3">
         <v>45900</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T58" s="3">
+      <c r="T58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U58" s="3">
         <v>45700</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X58" s="3">
+      <c r="X58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y58" s="3">
         <v>45500</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AA58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB58" s="3">
         <v>252000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>251800</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>2700</v>
       </c>
       <c r="AD58" s="3">
         <v>2700</v>
@@ -5561,399 +5695,411 @@
         <v>2700</v>
       </c>
       <c r="AG58" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="AH58" s="3">
         <v>2600</v>
       </c>
       <c r="AI58" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>3500</v>
-      </c>
-      <c r="AJ58" s="3">
-        <v>31700</v>
       </c>
       <c r="AK58" s="3">
         <v>31700</v>
       </c>
+      <c r="AL58" s="3">
+        <v>31700</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3">
         <v>20800</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="3">
         <v>12900</v>
       </c>
-      <c r="G59" s="3">
-        <v>27100</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3">
         <v>20500</v>
       </c>
-      <c r="I59" s="3">
-        <v>42200</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" s="3">
         <v>21100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>20500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>16000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>28800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>26300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>29500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>18700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>22600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>20900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>12800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>24500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>18100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>24000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>13700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>21300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>19800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>14500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>15300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>14300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>11700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>12500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>15700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>15600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>12700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>12400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>18300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="3">
         <v>83900</v>
       </c>
-      <c r="E60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F60" s="3">
+      <c r="F60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G60" s="3">
         <v>71500</v>
       </c>
-      <c r="G60" s="3">
-        <v>27100</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I60" s="3">
         <v>458800</v>
       </c>
-      <c r="I60" s="3">
-        <v>42200</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K60" s="3">
         <v>79100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>20500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>70300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>28800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>26300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>29500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>64900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>18700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>22600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>20900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>62800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>24500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>18100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>24000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>64600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>21300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>19800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>271500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>272700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>23300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>23400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>21900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>22900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>25400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>25000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>20000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>53100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>55400</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>277100</v>
       </c>
-      <c r="E61" s="3">
-        <v>331600</v>
-      </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>298900</v>
       </c>
-      <c r="G61" s="3">
-        <v>408000</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>431200</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>396300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>454400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>450800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>527500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>539000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>550500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>516000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>573400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>584800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>596300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>562000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>619100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>630400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>641800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>607700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>914400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>712000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>460400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>461100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>710500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>710900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>711300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>711700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>712100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>712300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>710900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>684700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>692400</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E62" s="3">
-        <v>33100</v>
-      </c>
-      <c r="F62" s="3">
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3">
         <v>2200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3">
+        <v>5300</v>
+      </c>
+      <c r="M62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="N62" s="3">
+        <v>2800</v>
+      </c>
+      <c r="O62" s="3">
+        <v>2900</v>
+      </c>
+      <c r="P62" s="3">
         <v>3000</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I62" s="3">
-        <v>2800</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K62" s="3">
-        <v>5300</v>
-      </c>
-      <c r="L62" s="3">
-        <v>2700</v>
-      </c>
-      <c r="M62" s="3">
-        <v>2800</v>
-      </c>
-      <c r="N62" s="3">
-        <v>2900</v>
-      </c>
-      <c r="O62" s="3">
-        <v>3000</v>
-      </c>
-      <c r="P62" s="3">
-        <v>3100</v>
       </c>
       <c r="Q62" s="3">
         <v>3100</v>
       </c>
       <c r="R62" s="3">
-        <v>3200</v>
+        <v>3100</v>
       </c>
       <c r="S62" s="3">
         <v>3200</v>
       </c>
       <c r="T62" s="3">
+        <v>3200</v>
+      </c>
+      <c r="U62" s="3">
         <v>4500</v>
-      </c>
-      <c r="U62" s="3">
-        <v>3200</v>
       </c>
       <c r="V62" s="3">
         <v>3200</v>
@@ -5974,37 +6120,40 @@
         <v>3200</v>
       </c>
       <c r="AB62" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="AC62" s="3">
         <v>3100</v>
       </c>
       <c r="AD62" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AE62" s="3">
         <v>1700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1100</v>
-      </c>
-      <c r="AI62" s="3">
-        <v>1000</v>
       </c>
       <c r="AJ62" s="3">
         <v>1000</v>
       </c>
       <c r="AK62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AL62" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="3">
         <v>362400</v>
       </c>
-      <c r="E66" s="3">
-        <v>364700</v>
-      </c>
-      <c r="F66" s="3">
+      <c r="F66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G66" s="3">
         <v>374200</v>
       </c>
-      <c r="G66" s="3">
-        <v>438100</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I66" s="3">
         <v>460700</v>
       </c>
-      <c r="I66" s="3">
-        <v>476200</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K66" s="3">
         <v>477700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>480200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>523800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>559200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>568200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>583000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>584000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>595200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>610600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>620400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>629300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>646800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>651800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>669000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>675500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>938800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>735000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>735100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>737000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>736900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>736000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>734700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>736000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>738700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>738400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>731900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>738800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>748800</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,37 +6849,40 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>126700</v>
+        <v>0</v>
       </c>
       <c r="E70" s="3">
         <v>126700</v>
       </c>
       <c r="F70" s="3">
-        <v>126700</v>
+        <v>0</v>
       </c>
       <c r="G70" s="3">
         <v>126700</v>
       </c>
       <c r="H70" s="3">
-        <v>126700</v>
+        <v>0</v>
       </c>
       <c r="I70" s="3">
         <v>126700</v>
       </c>
       <c r="J70" s="3">
-        <v>126700</v>
+        <v>0</v>
       </c>
       <c r="K70" s="3">
         <v>126700</v>
       </c>
       <c r="L70" s="3">
-        <v>126800</v>
+        <v>126700</v>
       </c>
       <c r="M70" s="3">
         <v>126800</v>
@@ -6729,7 +6897,7 @@
         <v>126800</v>
       </c>
       <c r="Q70" s="3">
-        <v>126700</v>
+        <v>126800</v>
       </c>
       <c r="R70" s="3">
         <v>126700</v>
@@ -6762,10 +6930,10 @@
         <v>126700</v>
       </c>
       <c r="AB70" s="3">
+        <v>126700</v>
+      </c>
+      <c r="AC70" s="3">
         <v>127100</v>
-      </c>
-      <c r="AC70" s="3">
-        <v>73200</v>
       </c>
       <c r="AD70" s="3">
         <v>73200</v>
@@ -6774,7 +6942,7 @@
         <v>73200</v>
       </c>
       <c r="AF70" s="3">
-        <v>73300</v>
+        <v>73200</v>
       </c>
       <c r="AG70" s="3">
         <v>73300</v>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>73300</v>
       </c>
+      <c r="AL70" s="3">
+        <v>73300</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,8 +7069,11 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6927,8 +7101,8 @@
       <c r="K72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L72" s="3">
-        <v>0</v>
+      <c r="L72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M72" s="3">
         <v>0</v>
@@ -7005,8 +7179,11 @@
       <c r="AK72" s="3">
         <v>0</v>
       </c>
+      <c r="AL72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="3">
         <v>358100</v>
       </c>
-      <c r="E76" s="3">
-        <v>349300</v>
-      </c>
-      <c r="F76" s="3">
+      <c r="F76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G76" s="3">
         <v>337500</v>
       </c>
-      <c r="G76" s="3">
-        <v>330000</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I76" s="3">
         <v>321500</v>
       </c>
-      <c r="I76" s="3">
-        <v>314000</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="J76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K76" s="3">
         <v>315500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>303900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>297100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>288400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>283900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>275700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>254700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>240700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>232300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>224000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>209800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>202000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>194600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>191100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>187000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>184400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>192000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>196200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>199400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>211800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>223000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>233200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>245100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>256100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>268900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>290700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>294500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>295800</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,150 +7729,156 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3">
         <v>14100</v>
       </c>
-      <c r="E81" s="3">
-        <v>15100</v>
-      </c>
-      <c r="F81" s="3">
+      <c r="F81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81" s="3">
         <v>10700</v>
       </c>
-      <c r="G81" s="3">
-        <v>11800</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="H81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" s="3">
         <v>10500</v>
       </c>
-      <c r="I81" s="3">
-        <v>1400</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="J81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" s="3">
         <v>14400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>9600</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>8</v>
       </c>
@@ -7693,12 +7888,12 @@
       <c r="O81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P81" s="3">
+      <c r="P81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q81" s="3">
         <v>16900</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>8</v>
       </c>
@@ -7726,41 +7921,44 @@
       <c r="Z81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AA81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-6900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>10000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>7900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,85 +7996,86 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3">
         <v>8100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3">
         <v>8000</v>
       </c>
-      <c r="F83" s="3">
-        <v>8000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>7900</v>
-      </c>
-      <c r="H83" s="3">
-        <v>8000</v>
+      <c r="H83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I83" s="3">
         <v>8000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K83" s="3">
         <v>7900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7800</v>
-      </c>
-      <c r="L83" s="3">
-        <v>8000</v>
       </c>
       <c r="M83" s="3">
         <v>8000</v>
       </c>
       <c r="N83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="O83" s="3">
         <v>7900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7800</v>
-      </c>
-      <c r="P83" s="3">
-        <v>8000</v>
       </c>
       <c r="Q83" s="3">
         <v>8000</v>
       </c>
       <c r="R83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="S83" s="3">
         <v>7900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>7800</v>
-      </c>
-      <c r="T83" s="3">
-        <v>8000</v>
       </c>
       <c r="U83" s="3">
         <v>8000</v>
       </c>
       <c r="V83" s="3">
-        <v>7900</v>
+        <v>8000</v>
       </c>
       <c r="W83" s="3">
         <v>7900</v>
       </c>
       <c r="X83" s="3">
+        <v>7900</v>
+      </c>
+      <c r="Y83" s="3">
         <v>8000</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>7600</v>
       </c>
       <c r="Z83" s="3">
         <v>7600</v>
       </c>
       <c r="AA83" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AB83" s="3">
         <v>7500</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>7600</v>
       </c>
       <c r="AC83" s="3">
         <v>7600</v>
@@ -7885,10 +8084,10 @@
         <v>7600</v>
       </c>
       <c r="AE83" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AF83" s="3">
         <v>7500</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>7600</v>
       </c>
       <c r="AG83" s="3">
         <v>7600</v>
@@ -7897,16 +8096,19 @@
         <v>7600</v>
       </c>
       <c r="AI83" s="3">
+        <v>7600</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>7500</v>
-      </c>
-      <c r="AJ83" s="3">
-        <v>7600</v>
       </c>
       <c r="AK83" s="3">
         <v>7600</v>
       </c>
+      <c r="AL83" s="3">
+        <v>7600</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3">
         <v>32500</v>
       </c>
-      <c r="E89" s="3">
-        <v>25600</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="3">
         <v>22500</v>
       </c>
-      <c r="G89" s="3">
-        <v>11600</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" s="3">
         <v>20200</v>
       </c>
-      <c r="I89" s="3">
-        <v>21800</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K89" s="3">
         <v>8800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>13700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>13400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>10900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>8200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>24800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>21000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>19800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>15800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>22900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>14200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>27600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>8100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>18700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>13500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>13600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>7000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>9200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>9000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>13500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>8600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>11900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>15000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>14800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>11400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>18200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>23300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>27000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,58 +8806,59 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3">
         <v>-2800</v>
       </c>
-      <c r="I91" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>8</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>8</v>
@@ -8645,8 +8866,8 @@
       <c r="U91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -8660,17 +8881,17 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>8</v>
+      <c r="AD91" s="3">
+        <v>0</v>
       </c>
       <c r="AE91" s="3" t="s">
         <v>8</v>
@@ -8684,17 +8905,20 @@
       <c r="AH91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI91" s="3">
-        <v>0</v>
+      <c r="AI91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
       <c r="AK91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,50 +9134,53 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3">
         <v>-2800</v>
       </c>
-      <c r="I94" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="J94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>8</v>
       </c>
@@ -8960,8 +9190,8 @@
       <c r="S94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
@@ -8991,11 +9221,11 @@
         <v>0</v>
       </c>
       <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-400</v>
       </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
       <c r="AF94" s="3">
         <v>0</v>
       </c>
@@ -9012,10 +9242,13 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL94" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,8 +9286,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9067,8 +9301,8 @@
       <c r="F96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="3">
-        <v>3300</v>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>8</v>
@@ -9079,12 +9313,12 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3">
         <v>2900</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -9119,19 +9353,19 @@
         <v>0</v>
       </c>
       <c r="X96" s="3">
-        <v>-2900</v>
+        <v>0</v>
       </c>
       <c r="Y96" s="3">
         <v>-2900</v>
       </c>
       <c r="Z96" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-5500</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-10600</v>
       </c>
       <c r="AC96" s="3">
         <v>-10600</v>
@@ -9140,7 +9374,7 @@
         <v>-10600</v>
       </c>
       <c r="AE96" s="3">
-        <v>-16700</v>
+        <v>-10600</v>
       </c>
       <c r="AF96" s="3">
         <v>-16700</v>
@@ -9160,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>-16700</v>
       </c>
+      <c r="AL96" s="3">
+        <v>-16700</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,106 +9724,109 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3">
         <v>-16300</v>
       </c>
-      <c r="E100" s="3">
-        <v>-9100</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="3">
         <v>-63100</v>
       </c>
-      <c r="G100" s="3">
-        <v>-9100</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3">
         <v>-8500</v>
       </c>
-      <c r="I100" s="3">
-        <v>-8400</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K100" s="3">
         <v>-8800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-40600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-29200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-12400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-14100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-15200</v>
-      </c>
-      <c r="P100" s="3">
-        <v>-15300</v>
       </c>
       <c r="Q100" s="3">
         <v>-15300</v>
       </c>
       <c r="R100" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="S100" s="3">
         <v>-13100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-13800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-15200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-14800</v>
-      </c>
-      <c r="V100" s="3">
-        <v>-14900</v>
       </c>
       <c r="W100" s="3">
         <v>-14900</v>
       </c>
       <c r="X100" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-264900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>191200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-6300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-6800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>41400</v>
-      </c>
-      <c r="AC100" s="3">
-        <v>-11800</v>
       </c>
       <c r="AD100" s="3">
         <v>-11800</v>
       </c>
       <c r="AE100" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-17900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-18100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-18600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>12000</v>
-      </c>
-      <c r="AI100" s="3">
-        <v>-24800</v>
       </c>
       <c r="AJ100" s="3">
         <v>-24800</v>
@@ -9588,8 +9834,11 @@
       <c r="AK100" s="3">
         <v>-24800</v>
       </c>
+      <c r="AL100" s="3">
+        <v>-24800</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9617,8 +9866,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9695,111 +9944,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>16100</v>
       </c>
-      <c r="E102" s="3">
-        <v>16500</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-40600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>8800</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="M102" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="N102" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="O102" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="P102" s="3">
+        <v>9600</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>5700</v>
+      </c>
+      <c r="R102" s="3">
+        <v>4500</v>
+      </c>
+      <c r="S102" s="3">
+        <v>2700</v>
+      </c>
+      <c r="T102" s="3">
+        <v>9100</v>
+      </c>
+      <c r="U102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="V102" s="3">
+        <v>12800</v>
+      </c>
+      <c r="W102" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="X102" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Y102" s="3">
+        <v>-251400</v>
+      </c>
+      <c r="Z102" s="3">
+        <v>204700</v>
+      </c>
+      <c r="AA102" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB102" s="3">
         <v>2400</v>
       </c>
-      <c r="H102" s="3">
-        <v>8800</v>
-      </c>
-      <c r="I102" s="3">
-        <v>12000</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-27000</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-17900</v>
-      </c>
-      <c r="M102" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="N102" s="3">
-        <v>-6400</v>
-      </c>
-      <c r="O102" s="3">
-        <v>9600</v>
-      </c>
-      <c r="P102" s="3">
-        <v>5700</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>4500</v>
-      </c>
-      <c r="R102" s="3">
-        <v>2700</v>
-      </c>
-      <c r="S102" s="3">
-        <v>9100</v>
-      </c>
-      <c r="T102" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="U102" s="3">
-        <v>12800</v>
-      </c>
-      <c r="V102" s="3">
-        <v>-6800</v>
-      </c>
-      <c r="W102" s="3">
-        <v>3800</v>
-      </c>
-      <c r="X102" s="3">
-        <v>-251400</v>
-      </c>
-      <c r="Y102" s="3">
-        <v>204700</v>
-      </c>
-      <c r="Z102" s="3">
-        <v>600</v>
-      </c>
-      <c r="AA102" s="3">
-        <v>2400</v>
-      </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>50400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-6100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-3100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-3800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>23400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-6700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1800</v>
       </c>
     </row>
